--- a/research/traditional_assets/database/data/romania/romania_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_real_estate_development.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07818100518361785</v>
+        <v>0.07809371557532406</v>
       </c>
       <c r="C2">
-        <v>620.449389667568</v>
+        <v>614.6524888509169</v>
       </c>
       <c r="D2">
-        <v>482.0493896675679</v>
+        <v>482.280488850917</v>
       </c>
       <c r="E2">
-        <v>-263.2</v>
+        <v>-257.172</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.028</v>
       </c>
       <c r="G2">
         <v>138.4</v>
@@ -1579,28 +1579,28 @@
         <v>117.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3032084</v>
       </c>
       <c r="N2">
-        <v>117.6</v>
+        <v>117.2967916</v>
       </c>
       <c r="O2">
-        <v>18.816</v>
+        <v>18.767486656</v>
       </c>
       <c r="P2">
-        <v>98.78399999999999</v>
+        <v>98.52930494399999</v>
       </c>
       <c r="Q2">
-        <v>99.78399999999999</v>
+        <v>99.52930494399999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07818100518361785</v>
+        <v>0.07845575310638794</v>
       </c>
       <c r="T2">
-        <v>0.4457367247241993</v>
+        <v>0.4495187332976168</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>387.8520515922382</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07809371557532406</v>
+        <v>0.07800642596703028</v>
       </c>
       <c r="C3">
-        <v>614.6524888509169</v>
+        <v>608.8558097229547</v>
       </c>
       <c r="D3">
-        <v>482.280488850917</v>
+        <v>482.5118097229548</v>
       </c>
       <c r="E3">
-        <v>-257.172</v>
+        <v>-251.144</v>
       </c>
       <c r="F3">
-        <v>6.028</v>
+        <v>12.056</v>
       </c>
       <c r="G3">
         <v>138.4</v>
@@ -1661,28 +1661,28 @@
         <v>117.6</v>
       </c>
       <c r="M3">
-        <v>0.3032084</v>
+        <v>0.6064168</v>
       </c>
       <c r="N3">
-        <v>117.2967916</v>
+        <v>116.9935832</v>
       </c>
       <c r="O3">
-        <v>18.767486656</v>
+        <v>18.718973312</v>
       </c>
       <c r="P3">
-        <v>98.52930494399999</v>
+        <v>98.27460988799999</v>
       </c>
       <c r="Q3">
-        <v>99.52930494399999</v>
+        <v>99.27460988799999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07845575310638794</v>
+        <v>0.07873610812962273</v>
       </c>
       <c r="T3">
-        <v>0.4495187332976168</v>
+        <v>0.4533779257194713</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>387.8520515922382</v>
+        <v>193.9260257961191</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07800642596703028</v>
+        <v>0.07791913635873648</v>
       </c>
       <c r="C4">
-        <v>608.8558097229547</v>
+        <v>603.0593526028267</v>
       </c>
       <c r="D4">
-        <v>482.5118097229548</v>
+        <v>482.7433526028267</v>
       </c>
       <c r="E4">
-        <v>-251.144</v>
+        <v>-245.116</v>
       </c>
       <c r="F4">
-        <v>12.056</v>
+        <v>18.084</v>
       </c>
       <c r="G4">
         <v>138.4</v>
@@ -1743,28 +1743,28 @@
         <v>117.6</v>
       </c>
       <c r="M4">
-        <v>0.6064168</v>
+        <v>0.9096251999999999</v>
       </c>
       <c r="N4">
-        <v>116.9935832</v>
+        <v>116.6903748</v>
       </c>
       <c r="O4">
-        <v>18.718973312</v>
+        <v>18.670459968</v>
       </c>
       <c r="P4">
-        <v>98.27460988799999</v>
+        <v>98.019914832</v>
       </c>
       <c r="Q4">
-        <v>99.27460988799999</v>
+        <v>99.019914832</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07873610812962273</v>
+        <v>0.07902224366880051</v>
       </c>
       <c r="T4">
-        <v>0.4533779257194713</v>
+        <v>0.457316689119096</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>193.9260257961191</v>
+        <v>129.2840171974127</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07791913635873648</v>
+        <v>0.07783184675044269</v>
       </c>
       <c r="C5">
-        <v>603.0593526028267</v>
+        <v>597.2631178102907</v>
       </c>
       <c r="D5">
-        <v>482.7433526028267</v>
+        <v>482.9751178102907</v>
       </c>
       <c r="E5">
-        <v>-245.116</v>
+        <v>-239.088</v>
       </c>
       <c r="F5">
-        <v>18.084</v>
+        <v>24.112</v>
       </c>
       <c r="G5">
         <v>138.4</v>
@@ -1825,28 +1825,28 @@
         <v>117.6</v>
       </c>
       <c r="M5">
-        <v>0.9096251999999999</v>
+        <v>1.2128336</v>
       </c>
       <c r="N5">
-        <v>116.6903748</v>
+        <v>116.3871664</v>
       </c>
       <c r="O5">
-        <v>18.670459968</v>
+        <v>18.621946624</v>
       </c>
       <c r="P5">
-        <v>98.019914832</v>
+        <v>97.765219776</v>
       </c>
       <c r="Q5">
-        <v>99.019914832</v>
+        <v>98.765219776</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07902224366880051</v>
+        <v>0.07931434036504448</v>
       </c>
       <c r="T5">
-        <v>0.457316689119096</v>
+        <v>0.4613375100895462</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>129.2840171974127</v>
+        <v>96.96301289805956</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07783184675044269</v>
+        <v>0.07774455714214892</v>
       </c>
       <c r="C6">
-        <v>597.2631178102907</v>
+        <v>591.4671056657191</v>
       </c>
       <c r="D6">
-        <v>482.9751178102907</v>
+        <v>483.2071056657191</v>
       </c>
       <c r="E6">
-        <v>-239.088</v>
+        <v>-233.06</v>
       </c>
       <c r="F6">
-        <v>24.112</v>
+        <v>30.14</v>
       </c>
       <c r="G6">
         <v>138.4</v>
@@ -1907,28 +1907,28 @@
         <v>117.6</v>
       </c>
       <c r="M6">
-        <v>1.2128336</v>
+        <v>1.516042</v>
       </c>
       <c r="N6">
-        <v>116.3871664</v>
+        <v>116.083958</v>
       </c>
       <c r="O6">
-        <v>18.621946624</v>
+        <v>18.57343328</v>
       </c>
       <c r="P6">
-        <v>97.765219776</v>
+        <v>97.51052471999999</v>
       </c>
       <c r="Q6">
-        <v>98.765219776</v>
+        <v>98.51052471999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07931434036504448</v>
+        <v>0.07961258646541991</v>
       </c>
       <c r="T6">
-        <v>0.4613375100895462</v>
+        <v>0.4654429799225323</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>96.96301289805956</v>
+        <v>77.57041031844764</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07774455714214892</v>
+        <v>0.07765726753385513</v>
       </c>
       <c r="C7">
-        <v>591.4671056657191</v>
+        <v>585.6713164901004</v>
       </c>
       <c r="D7">
-        <v>483.2071056657191</v>
+        <v>483.4393164901004</v>
       </c>
       <c r="E7">
-        <v>-233.06</v>
+        <v>-227.032</v>
       </c>
       <c r="F7">
-        <v>30.14</v>
+        <v>36.168</v>
       </c>
       <c r="G7">
         <v>138.4</v>
@@ -1989,28 +1989,28 @@
         <v>117.6</v>
       </c>
       <c r="M7">
-        <v>1.516042</v>
+        <v>1.8192504</v>
       </c>
       <c r="N7">
-        <v>116.083958</v>
+        <v>115.7807496</v>
       </c>
       <c r="O7">
-        <v>18.57343328</v>
+        <v>18.524919936</v>
       </c>
       <c r="P7">
-        <v>97.51052471999999</v>
+        <v>97.25582966399999</v>
       </c>
       <c r="Q7">
-        <v>98.51052471999999</v>
+        <v>98.25582966399999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07961258646541991</v>
+        <v>0.07991717822750546</v>
       </c>
       <c r="T7">
-        <v>0.4654429799225323</v>
+        <v>0.4696358001774968</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>77.57041031844764</v>
+        <v>64.64200859870637</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07765726753385513</v>
+        <v>0.07756997792556133</v>
       </c>
       <c r="C8">
-        <v>585.6713164901004</v>
+        <v>579.8757506050399</v>
       </c>
       <c r="D8">
-        <v>483.4393164901004</v>
+        <v>483.67175060504</v>
       </c>
       <c r="E8">
-        <v>-227.032</v>
+        <v>-221.004</v>
       </c>
       <c r="F8">
-        <v>36.168</v>
+        <v>42.19599999999999</v>
       </c>
       <c r="G8">
         <v>138.4</v>
@@ -2071,28 +2071,28 @@
         <v>117.6</v>
       </c>
       <c r="M8">
-        <v>1.8192504</v>
+        <v>2.1224588</v>
       </c>
       <c r="N8">
-        <v>115.7807496</v>
+        <v>115.4775412</v>
       </c>
       <c r="O8">
-        <v>18.524919936</v>
+        <v>18.476406592</v>
       </c>
       <c r="P8">
-        <v>97.25582966399999</v>
+        <v>97.00113460799999</v>
       </c>
       <c r="Q8">
-        <v>98.25582966399999</v>
+        <v>98.00113460799999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07991717822750546</v>
+        <v>0.08022832035006595</v>
       </c>
       <c r="T8">
-        <v>0.4696358001774968</v>
+        <v>0.4739187886099874</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>64.64200859870637</v>
+        <v>55.40743594174833</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07756997792556133</v>
+        <v>0.07748268831726757</v>
       </c>
       <c r="C9">
-        <v>579.8757506050399</v>
+        <v>574.0804083327621</v>
       </c>
       <c r="D9">
-        <v>483.67175060504</v>
+        <v>483.9044083327621</v>
       </c>
       <c r="E9">
-        <v>-221.004</v>
+        <v>-214.976</v>
       </c>
       <c r="F9">
-        <v>42.196</v>
+        <v>48.224</v>
       </c>
       <c r="G9">
         <v>138.4</v>
@@ -2153,28 +2153,28 @@
         <v>117.6</v>
       </c>
       <c r="M9">
-        <v>2.1224588</v>
+        <v>2.4256672</v>
       </c>
       <c r="N9">
-        <v>115.4775412</v>
+        <v>115.1743328</v>
       </c>
       <c r="O9">
-        <v>18.476406592</v>
+        <v>18.427893248</v>
       </c>
       <c r="P9">
-        <v>97.00113460799999</v>
+        <v>96.74643955199998</v>
       </c>
       <c r="Q9">
-        <v>98.00113460799999</v>
+        <v>97.74643955199998</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08022832035006595</v>
+        <v>0.08054622643181256</v>
       </c>
       <c r="T9">
-        <v>0.4739187886099874</v>
+        <v>0.4782948854866625</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>55.40743594174831</v>
+        <v>48.48150644902977</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07748268831726757</v>
+        <v>0.07739539870897377</v>
       </c>
       <c r="C10">
-        <v>574.0804083327621</v>
+        <v>568.2852899961117</v>
       </c>
       <c r="D10">
-        <v>483.9044083327621</v>
+        <v>484.1372899961116</v>
       </c>
       <c r="E10">
-        <v>-214.976</v>
+        <v>-208.948</v>
       </c>
       <c r="F10">
-        <v>48.224</v>
+        <v>54.252</v>
       </c>
       <c r="G10">
         <v>138.4</v>
@@ -2235,28 +2235,28 @@
         <v>117.6</v>
       </c>
       <c r="M10">
-        <v>2.4256672</v>
+        <v>2.7288756</v>
       </c>
       <c r="N10">
-        <v>115.1743328</v>
+        <v>114.8711244</v>
       </c>
       <c r="O10">
-        <v>18.427893248</v>
+        <v>18.379379904</v>
       </c>
       <c r="P10">
-        <v>96.74643955199998</v>
+        <v>96.491744496</v>
       </c>
       <c r="Q10">
-        <v>97.74643955199998</v>
+        <v>97.491744496</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08054622643181256</v>
+        <v>0.08087111946041073</v>
       </c>
       <c r="T10">
-        <v>0.4782948854866625</v>
+        <v>0.4827671603166712</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>48.48150644902977</v>
+        <v>43.09467239913758</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07739539870897377</v>
+        <v>0.07730810910067996</v>
       </c>
       <c r="C11">
-        <v>568.2852899961117</v>
+        <v>562.4903959185551</v>
       </c>
       <c r="D11">
-        <v>484.1372899961116</v>
+        <v>484.3703959185551</v>
       </c>
       <c r="E11">
-        <v>-208.948</v>
+        <v>-202.92</v>
       </c>
       <c r="F11">
-        <v>54.252</v>
+        <v>60.27999999999999</v>
       </c>
       <c r="G11">
         <v>138.4</v>
@@ -2317,28 +2317,28 @@
         <v>117.6</v>
       </c>
       <c r="M11">
-        <v>2.7288756</v>
+        <v>3.032083999999999</v>
       </c>
       <c r="N11">
-        <v>114.8711244</v>
+        <v>114.567916</v>
       </c>
       <c r="O11">
-        <v>18.379379904</v>
+        <v>18.33086656</v>
       </c>
       <c r="P11">
-        <v>96.491744496</v>
+        <v>96.23704943999999</v>
       </c>
       <c r="Q11">
-        <v>97.491744496</v>
+        <v>97.23704943999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08087111946041073</v>
+        <v>0.08120323233408885</v>
       </c>
       <c r="T11">
-        <v>0.4827671603166712</v>
+        <v>0.4873388190317912</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>43.09467239913758</v>
+        <v>38.78520515922383</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07730810910067996</v>
+        <v>0.07722081949238617</v>
       </c>
       <c r="C12">
-        <v>562.4903959185551</v>
+        <v>556.6957264241819</v>
       </c>
       <c r="D12">
-        <v>484.3703959185551</v>
+        <v>484.6037264241818</v>
       </c>
       <c r="E12">
-        <v>-202.92</v>
+        <v>-196.892</v>
       </c>
       <c r="F12">
-        <v>60.28</v>
+        <v>66.30799999999999</v>
       </c>
       <c r="G12">
         <v>138.4</v>
@@ -2399,28 +2399,28 @@
         <v>117.6</v>
       </c>
       <c r="M12">
-        <v>3.032084</v>
+        <v>3.335292399999999</v>
       </c>
       <c r="N12">
-        <v>114.567916</v>
+        <v>114.2647076</v>
       </c>
       <c r="O12">
-        <v>18.33086656</v>
+        <v>18.282353216</v>
       </c>
       <c r="P12">
-        <v>96.23704943999999</v>
+        <v>95.98235438399999</v>
       </c>
       <c r="Q12">
-        <v>97.23704943999999</v>
+        <v>96.98235438399999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08120323233408885</v>
+        <v>0.08154280841841144</v>
       </c>
       <c r="T12">
-        <v>0.4873388190317912</v>
+        <v>0.4920132116506218</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>38.78520515922382</v>
+        <v>35.25927741747621</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07722081949238617</v>
+        <v>0.0771335298840924</v>
       </c>
       <c r="C13">
-        <v>556.6957264241819</v>
+        <v>550.9012818377065</v>
       </c>
       <c r="D13">
-        <v>484.6037264241818</v>
+        <v>484.8372818377065</v>
       </c>
       <c r="E13">
-        <v>-196.892</v>
+        <v>-190.864</v>
       </c>
       <c r="F13">
-        <v>66.30799999999999</v>
+        <v>72.336</v>
       </c>
       <c r="G13">
         <v>138.4</v>
@@ -2481,28 +2481,28 @@
         <v>117.6</v>
       </c>
       <c r="M13">
-        <v>3.335292399999999</v>
+        <v>3.6385008</v>
       </c>
       <c r="N13">
-        <v>114.2647076</v>
+        <v>113.9614992</v>
       </c>
       <c r="O13">
-        <v>18.282353216</v>
+        <v>18.233839872</v>
       </c>
       <c r="P13">
-        <v>95.98235438399999</v>
+        <v>95.72765932799999</v>
       </c>
       <c r="Q13">
-        <v>96.98235438399999</v>
+        <v>96.72765932799999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08154280841841144</v>
+        <v>0.08189010214101408</v>
       </c>
       <c r="T13">
-        <v>0.4920132116506218</v>
+        <v>0.4967938404653348</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>35.25927741747621</v>
+        <v>32.32100429935318</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0771335298840924</v>
+        <v>0.07704624027579861</v>
       </c>
       <c r="C14">
-        <v>550.9012818377065</v>
+        <v>545.10706248447</v>
       </c>
       <c r="D14">
-        <v>484.8372818377065</v>
+        <v>485.07106248447</v>
       </c>
       <c r="E14">
-        <v>-190.864</v>
+        <v>-184.836</v>
       </c>
       <c r="F14">
-        <v>72.336</v>
+        <v>78.36399999999999</v>
       </c>
       <c r="G14">
         <v>138.4</v>
@@ -2563,28 +2563,28 @@
         <v>117.6</v>
       </c>
       <c r="M14">
-        <v>3.6385008</v>
+        <v>3.941709199999999</v>
       </c>
       <c r="N14">
-        <v>113.9614992</v>
+        <v>113.6582908</v>
       </c>
       <c r="O14">
-        <v>18.233839872</v>
+        <v>18.185326528</v>
       </c>
       <c r="P14">
-        <v>95.72765932799999</v>
+        <v>95.47296427199998</v>
       </c>
       <c r="Q14">
-        <v>96.72765932799999</v>
+        <v>96.47296427199998</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08189010214101408</v>
+        <v>0.08224537962735472</v>
       </c>
       <c r="T14">
-        <v>0.4967938404653348</v>
+        <v>0.5016843687930298</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>32.32100429935318</v>
+        <v>29.83477319940294</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07704624027579861</v>
+        <v>0.07695895066750481</v>
       </c>
       <c r="C15">
-        <v>545.10706248447</v>
+        <v>539.3130686904408</v>
       </c>
       <c r="D15">
-        <v>485.07106248447</v>
+        <v>485.3050686904409</v>
       </c>
       <c r="E15">
-        <v>-184.836</v>
+        <v>-178.808</v>
       </c>
       <c r="F15">
-        <v>78.36399999999999</v>
+        <v>84.392</v>
       </c>
       <c r="G15">
         <v>138.4</v>
@@ -2645,28 +2645,28 @@
         <v>117.6</v>
       </c>
       <c r="M15">
-        <v>3.941709199999999</v>
+        <v>4.2449176</v>
       </c>
       <c r="N15">
-        <v>113.6582908</v>
+        <v>113.3550824</v>
       </c>
       <c r="O15">
-        <v>18.185326528</v>
+        <v>18.136813184</v>
       </c>
       <c r="P15">
-        <v>95.47296427199998</v>
+        <v>95.218269216</v>
       </c>
       <c r="Q15">
-        <v>96.47296427199998</v>
+        <v>96.218269216</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08224537962735472</v>
+        <v>0.08260891938081956</v>
       </c>
       <c r="T15">
-        <v>0.5016843687930298</v>
+        <v>0.506688630337648</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>29.83477319940294</v>
+        <v>27.70371797087416</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07695895066750481</v>
+        <v>0.07687166105921103</v>
       </c>
       <c r="C16">
-        <v>539.3130686904408</v>
+        <v>533.519300782217</v>
       </c>
       <c r="D16">
-        <v>485.3050686904409</v>
+        <v>485.539300782217</v>
       </c>
       <c r="E16">
-        <v>-178.808</v>
+        <v>-172.78</v>
       </c>
       <c r="F16">
-        <v>84.392</v>
+        <v>90.42</v>
       </c>
       <c r="G16">
         <v>138.4</v>
@@ -2727,28 +2727,28 @@
         <v>117.6</v>
       </c>
       <c r="M16">
-        <v>4.2449176</v>
+        <v>4.548126</v>
       </c>
       <c r="N16">
-        <v>113.3550824</v>
+        <v>113.051874</v>
       </c>
       <c r="O16">
-        <v>18.136813184</v>
+        <v>18.08829984</v>
       </c>
       <c r="P16">
-        <v>95.218269216</v>
+        <v>94.96357415999999</v>
       </c>
       <c r="Q16">
-        <v>96.218269216</v>
+        <v>95.96357415999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08260891938081956</v>
+        <v>0.0829810130108365</v>
       </c>
       <c r="T16">
-        <v>0.506688630337648</v>
+        <v>0.5118106392127276</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>27.70371797087416</v>
+        <v>25.85680343948255</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07687166105921103</v>
+        <v>0.07678437145091724</v>
       </c>
       <c r="C17">
-        <v>533.519300782217</v>
+        <v>527.725759087027</v>
       </c>
       <c r="D17">
-        <v>485.539300782217</v>
+        <v>485.773759087027</v>
       </c>
       <c r="E17">
-        <v>-172.78</v>
+        <v>-166.752</v>
       </c>
       <c r="F17">
-        <v>90.41999999999999</v>
+        <v>96.44799999999999</v>
       </c>
       <c r="G17">
         <v>138.4</v>
@@ -2809,28 +2809,28 @@
         <v>117.6</v>
       </c>
       <c r="M17">
-        <v>4.548125999999999</v>
+        <v>4.8513344</v>
       </c>
       <c r="N17">
-        <v>113.051874</v>
+        <v>112.7486656</v>
       </c>
       <c r="O17">
-        <v>18.08829984</v>
+        <v>18.039786496</v>
       </c>
       <c r="P17">
-        <v>94.96357415999999</v>
+        <v>94.70887910399999</v>
       </c>
       <c r="Q17">
-        <v>95.96357415999999</v>
+        <v>95.70887910399999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0829810130108365</v>
+        <v>0.08336196601299671</v>
       </c>
       <c r="T17">
-        <v>0.5118106392127276</v>
+        <v>0.5170546006800711</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>25.85680343948255</v>
+        <v>24.24075322451489</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07678437145091724</v>
+        <v>0.07669708184262344</v>
       </c>
       <c r="C18">
-        <v>527.725759087027</v>
+        <v>521.9324439327321</v>
       </c>
       <c r="D18">
-        <v>485.773759087027</v>
+        <v>486.0084439327321</v>
       </c>
       <c r="E18">
-        <v>-166.752</v>
+        <v>-160.724</v>
       </c>
       <c r="F18">
-        <v>96.44799999999999</v>
+        <v>102.476</v>
       </c>
       <c r="G18">
         <v>138.4</v>
@@ -2891,28 +2891,28 @@
         <v>117.6</v>
       </c>
       <c r="M18">
-        <v>4.8513344</v>
+        <v>5.1545428</v>
       </c>
       <c r="N18">
-        <v>112.7486656</v>
+        <v>112.4454572</v>
       </c>
       <c r="O18">
-        <v>18.039786496</v>
+        <v>17.991273152</v>
       </c>
       <c r="P18">
-        <v>94.70887910399999</v>
+        <v>94.454184048</v>
       </c>
       <c r="Q18">
-        <v>95.70887910399999</v>
+        <v>95.454184048</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08336196601299671</v>
+        <v>0.08375209860557042</v>
       </c>
       <c r="T18">
-        <v>0.5170546006800711</v>
+        <v>0.5224249226647001</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>24.24075322451489</v>
+        <v>22.81482656424931</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07669708184262344</v>
+        <v>0.07660979223432966</v>
       </c>
       <c r="C19">
-        <v>521.9324439327321</v>
+        <v>516.1393556478272</v>
       </c>
       <c r="D19">
-        <v>486.0084439327321</v>
+        <v>486.2433556478272</v>
       </c>
       <c r="E19">
-        <v>-160.724</v>
+        <v>-154.696</v>
       </c>
       <c r="F19">
-        <v>102.476</v>
+        <v>108.504</v>
       </c>
       <c r="G19">
         <v>138.4</v>
@@ -2973,28 +2973,28 @@
         <v>117.6</v>
       </c>
       <c r="M19">
-        <v>5.1545428</v>
+        <v>5.4577512</v>
       </c>
       <c r="N19">
-        <v>112.4454572</v>
+        <v>112.1422488</v>
       </c>
       <c r="O19">
-        <v>17.991273152</v>
+        <v>17.942759808</v>
       </c>
       <c r="P19">
-        <v>94.454184048</v>
+        <v>94.199488992</v>
       </c>
       <c r="Q19">
-        <v>95.454184048</v>
+        <v>95.199488992</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08375209860557042</v>
+        <v>0.08415174662723129</v>
       </c>
       <c r="T19">
-        <v>0.5224249226647001</v>
+        <v>0.5279262281123687</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>22.81482656424931</v>
+        <v>21.54733619956879</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07660979223432968</v>
+        <v>0.07652250262603587</v>
       </c>
       <c r="C20">
-        <v>516.1393556478272</v>
+        <v>510.3464945614427</v>
       </c>
       <c r="D20">
-        <v>486.2433556478272</v>
+        <v>486.4784945614427</v>
       </c>
       <c r="E20">
-        <v>-154.696</v>
+        <v>-148.668</v>
       </c>
       <c r="F20">
-        <v>108.504</v>
+        <v>114.532</v>
       </c>
       <c r="G20">
         <v>138.4</v>
@@ -3055,28 +3055,28 @@
         <v>117.6</v>
       </c>
       <c r="M20">
-        <v>5.4577512</v>
+        <v>5.7609596</v>
       </c>
       <c r="N20">
-        <v>112.1422488</v>
+        <v>111.8390404</v>
       </c>
       <c r="O20">
-        <v>17.942759808</v>
+        <v>17.894246464</v>
       </c>
       <c r="P20">
-        <v>94.199488992</v>
+        <v>93.944793936</v>
       </c>
       <c r="Q20">
-        <v>95.199488992</v>
+        <v>94.944793936</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08415174662723129</v>
+        <v>0.08456126250127885</v>
       </c>
       <c r="T20">
-        <v>0.5279262281123687</v>
+        <v>0.5335633682624489</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>21.54733619956879</v>
+        <v>20.41326587327569</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07652250262603587</v>
+        <v>0.07643521301774209</v>
       </c>
       <c r="C21">
-        <v>510.3464945614427</v>
+        <v>504.5538610033461</v>
       </c>
       <c r="D21">
-        <v>486.4784945614427</v>
+        <v>486.713861003346</v>
       </c>
       <c r="E21">
-        <v>-148.668</v>
+        <v>-142.64</v>
       </c>
       <c r="F21">
-        <v>114.532</v>
+        <v>120.56</v>
       </c>
       <c r="G21">
         <v>138.4</v>
@@ -3137,28 +3137,28 @@
         <v>117.6</v>
       </c>
       <c r="M21">
-        <v>5.7609596</v>
+        <v>6.064168</v>
       </c>
       <c r="N21">
-        <v>111.8390404</v>
+        <v>111.535832</v>
       </c>
       <c r="O21">
-        <v>17.894246464</v>
+        <v>17.84573312</v>
       </c>
       <c r="P21">
-        <v>93.944793936</v>
+        <v>93.69009887999999</v>
       </c>
       <c r="Q21">
-        <v>94.944793936</v>
+        <v>94.69009887999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08456126250127885</v>
+        <v>0.08498101627217761</v>
       </c>
       <c r="T21">
-        <v>0.5335633682624489</v>
+        <v>0.5393414369162811</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>20.41326587327569</v>
+        <v>19.39260257961191</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07643521301774209</v>
+        <v>0.07634792340944831</v>
       </c>
       <c r="C22">
-        <v>504.5538610033461</v>
+        <v>498.761455303943</v>
       </c>
       <c r="D22">
-        <v>486.713861003346</v>
+        <v>486.949455303943</v>
       </c>
       <c r="E22">
-        <v>-142.64</v>
+        <v>-136.612</v>
       </c>
       <c r="F22">
-        <v>120.56</v>
+        <v>126.588</v>
       </c>
       <c r="G22">
         <v>138.4</v>
@@ -3219,28 +3219,28 @@
         <v>117.6</v>
       </c>
       <c r="M22">
-        <v>6.064168</v>
+        <v>6.3673764</v>
       </c>
       <c r="N22">
-        <v>111.535832</v>
+        <v>111.2326236</v>
       </c>
       <c r="O22">
-        <v>17.84573312</v>
+        <v>17.797219776</v>
       </c>
       <c r="P22">
-        <v>93.69009887999999</v>
+        <v>93.43540382399999</v>
       </c>
       <c r="Q22">
-        <v>94.69009887999999</v>
+        <v>94.43540382399999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08498101627217761</v>
+        <v>0.08541139672082063</v>
       </c>
       <c r="T22">
-        <v>0.5393414369162811</v>
+        <v>0.5452657857891977</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>19.39260257961191</v>
+        <v>18.4691453139161</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07634792340944829</v>
+        <v>0.0762606338011545</v>
       </c>
       <c r="C23">
-        <v>498.7614553039431</v>
+        <v>492.9692777942795</v>
       </c>
       <c r="D23">
-        <v>486.949455303943</v>
+        <v>487.1852777942794</v>
       </c>
       <c r="E23">
-        <v>-136.612</v>
+        <v>-130.584</v>
       </c>
       <c r="F23">
-        <v>126.588</v>
+        <v>132.616</v>
       </c>
       <c r="G23">
         <v>138.4</v>
@@ -3301,28 +3301,28 @@
         <v>117.6</v>
       </c>
       <c r="M23">
-        <v>6.367376399999999</v>
+        <v>6.670584799999999</v>
       </c>
       <c r="N23">
-        <v>111.2326236</v>
+        <v>110.9294152</v>
       </c>
       <c r="O23">
-        <v>17.797219776</v>
+        <v>17.748706432</v>
       </c>
       <c r="P23">
-        <v>93.43540382399999</v>
+        <v>93.18070876799999</v>
       </c>
       <c r="Q23">
-        <v>94.43540382399999</v>
+        <v>94.18070876799999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08541139672082063</v>
+        <v>0.08585281256558269</v>
       </c>
       <c r="T23">
-        <v>0.5452657857891977</v>
+        <v>0.5513420410434711</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>18.46914531391611</v>
+        <v>17.6296387087381</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0762606338011545</v>
+        <v>0.07617334419286073</v>
       </c>
       <c r="C24">
-        <v>492.9692777942795</v>
+        <v>487.1773288060427</v>
       </c>
       <c r="D24">
-        <v>487.1852777942794</v>
+        <v>487.4213288060428</v>
       </c>
       <c r="E24">
-        <v>-130.584</v>
+        <v>-124.556</v>
       </c>
       <c r="F24">
-        <v>132.616</v>
+        <v>138.644</v>
       </c>
       <c r="G24">
         <v>138.4</v>
@@ -3383,28 +3383,28 @@
         <v>117.6</v>
       </c>
       <c r="M24">
-        <v>6.670584799999999</v>
+        <v>6.9737932</v>
       </c>
       <c r="N24">
-        <v>110.9294152</v>
+        <v>110.6262068</v>
       </c>
       <c r="O24">
-        <v>17.748706432</v>
+        <v>17.700193088</v>
       </c>
       <c r="P24">
-        <v>93.18070876799999</v>
+        <v>92.92601371199999</v>
       </c>
       <c r="Q24">
-        <v>94.18070876799999</v>
+        <v>93.92601371199999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08585281256558269</v>
+        <v>0.08630569375696198</v>
       </c>
       <c r="T24">
-        <v>0.5513420410434711</v>
+        <v>0.5575761211095439</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>17.6296387087381</v>
+        <v>16.8631326779234</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07617334419286073</v>
+        <v>0.07608605458456694</v>
       </c>
       <c r="C25">
-        <v>487.1773288060427</v>
+        <v>481.3856086715638</v>
       </c>
       <c r="D25">
-        <v>487.4213288060428</v>
+        <v>487.6576086715638</v>
       </c>
       <c r="E25">
-        <v>-124.556</v>
+        <v>-118.528</v>
       </c>
       <c r="F25">
-        <v>138.644</v>
+        <v>144.672</v>
       </c>
       <c r="G25">
         <v>138.4</v>
@@ -3465,28 +3465,28 @@
         <v>117.6</v>
       </c>
       <c r="M25">
-        <v>6.9737932</v>
+        <v>7.277001599999999</v>
       </c>
       <c r="N25">
-        <v>110.6262068</v>
+        <v>110.3229984</v>
       </c>
       <c r="O25">
-        <v>17.700193088</v>
+        <v>17.651679744</v>
       </c>
       <c r="P25">
-        <v>92.92601371199999</v>
+        <v>92.67131865599998</v>
       </c>
       <c r="Q25">
-        <v>93.92601371199999</v>
+        <v>93.67131865599998</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08630569375696198</v>
+        <v>0.08677049287443017</v>
       </c>
       <c r="T25">
-        <v>0.5575761211095439</v>
+        <v>0.5639742559141975</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>16.8631326779234</v>
+        <v>16.16050214967659</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07608605458456692</v>
+        <v>0.07599876497627314</v>
       </c>
       <c r="C26">
-        <v>481.3856086715638</v>
+        <v>475.5941177238178</v>
       </c>
       <c r="D26">
-        <v>487.6576086715638</v>
+        <v>487.8941177238177</v>
       </c>
       <c r="E26">
-        <v>-118.528</v>
+        <v>-112.5</v>
       </c>
       <c r="F26">
-        <v>144.672</v>
+        <v>150.7</v>
       </c>
       <c r="G26">
         <v>138.4</v>
@@ -3547,28 +3547,28 @@
         <v>117.6</v>
       </c>
       <c r="M26">
-        <v>7.277001599999999</v>
+        <v>7.580209999999999</v>
       </c>
       <c r="N26">
-        <v>110.3229984</v>
+        <v>110.01979</v>
       </c>
       <c r="O26">
-        <v>17.651679744</v>
+        <v>17.6031664</v>
       </c>
       <c r="P26">
-        <v>92.67131865599998</v>
+        <v>92.41662360000001</v>
       </c>
       <c r="Q26">
-        <v>93.67131865599998</v>
+        <v>93.41662360000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08677049287443017</v>
+        <v>0.08724768663503085</v>
       </c>
       <c r="T26">
-        <v>0.5639742559141975</v>
+        <v>0.5705430076469751</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.16050214967659</v>
+        <v>15.51408206368953</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07599876497627314</v>
+        <v>0.07591147536797936</v>
       </c>
       <c r="C27">
-        <v>475.5941177238178</v>
+        <v>469.8028562964262</v>
       </c>
       <c r="D27">
-        <v>487.8941177238177</v>
+        <v>488.1308562964261</v>
       </c>
       <c r="E27">
-        <v>-112.5</v>
+        <v>-106.472</v>
       </c>
       <c r="F27">
-        <v>150.7</v>
+        <v>156.728</v>
       </c>
       <c r="G27">
         <v>138.4</v>
@@ -3629,28 +3629,28 @@
         <v>117.6</v>
       </c>
       <c r="M27">
-        <v>7.580209999999999</v>
+        <v>7.883418399999998</v>
       </c>
       <c r="N27">
-        <v>110.01979</v>
+        <v>109.7165816</v>
       </c>
       <c r="O27">
-        <v>17.6031664</v>
+        <v>17.554653056</v>
       </c>
       <c r="P27">
-        <v>92.41662360000001</v>
+        <v>92.16192854400001</v>
       </c>
       <c r="Q27">
-        <v>93.41662360000001</v>
+        <v>93.16192854400001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08724768663503085</v>
+        <v>0.08773777752429643</v>
       </c>
       <c r="T27">
-        <v>0.5705430076469751</v>
+        <v>0.5772892932103684</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.51408206368953</v>
+        <v>14.91738659970147</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07591147536797936</v>
+        <v>0.07582418575968555</v>
       </c>
       <c r="C28">
-        <v>469.8028562964262</v>
+        <v>464.0118247236587</v>
       </c>
       <c r="D28">
-        <v>488.1308562964261</v>
+        <v>488.3678247236587</v>
       </c>
       <c r="E28">
-        <v>-106.472</v>
+        <v>-100.444</v>
       </c>
       <c r="F28">
-        <v>156.728</v>
+        <v>162.756</v>
       </c>
       <c r="G28">
         <v>138.4</v>
@@ -3711,28 +3711,28 @@
         <v>117.6</v>
       </c>
       <c r="M28">
-        <v>7.883418399999998</v>
+        <v>8.186626799999999</v>
       </c>
       <c r="N28">
-        <v>109.7165816</v>
+        <v>109.4133732</v>
       </c>
       <c r="O28">
-        <v>17.554653056</v>
+        <v>17.506139712</v>
       </c>
       <c r="P28">
-        <v>92.16192854400001</v>
+        <v>91.907233488</v>
       </c>
       <c r="Q28">
-        <v>93.16192854400001</v>
+        <v>92.907233488</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08773777752429643</v>
+        <v>0.0882412955612131</v>
       </c>
       <c r="T28">
-        <v>0.5772892932103684</v>
+        <v>0.5842204085152245</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>14.91738659970147</v>
+        <v>14.36489079971253</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07582418575968555</v>
+        <v>0.07573689615139179</v>
       </c>
       <c r="C29">
-        <v>464.0118247236587</v>
+        <v>458.2210233404339</v>
       </c>
       <c r="D29">
-        <v>488.3678247236587</v>
+        <v>488.6050233404339</v>
       </c>
       <c r="E29">
-        <v>-100.444</v>
+        <v>-94.416</v>
       </c>
       <c r="F29">
-        <v>162.756</v>
+        <v>168.784</v>
       </c>
       <c r="G29">
         <v>138.4</v>
@@ -3793,28 +3793,28 @@
         <v>117.6</v>
       </c>
       <c r="M29">
-        <v>8.186626799999999</v>
+        <v>8.4898352</v>
       </c>
       <c r="N29">
-        <v>109.4133732</v>
+        <v>109.1101648</v>
       </c>
       <c r="O29">
-        <v>17.506139712</v>
+        <v>17.457626368</v>
       </c>
       <c r="P29">
-        <v>91.907233488</v>
+        <v>91.652538432</v>
       </c>
       <c r="Q29">
-        <v>92.907233488</v>
+        <v>92.652538432</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0882412955612131</v>
+        <v>0.08875880021026636</v>
       </c>
       <c r="T29">
-        <v>0.5842204085152245</v>
+        <v>0.591344054800771</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.36489079971253</v>
+        <v>13.85185898543708</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07573689615139179</v>
+        <v>0.07564960654309799</v>
       </c>
       <c r="C30">
-        <v>458.2210233404339</v>
+        <v>452.4304524823218</v>
       </c>
       <c r="D30">
-        <v>488.6050233404339</v>
+        <v>488.8424524823218</v>
       </c>
       <c r="E30">
-        <v>-94.416</v>
+        <v>-88.38799999999998</v>
       </c>
       <c r="F30">
-        <v>168.784</v>
+        <v>174.812</v>
       </c>
       <c r="G30">
         <v>138.4</v>
@@ -3875,28 +3875,28 @@
         <v>117.6</v>
       </c>
       <c r="M30">
-        <v>8.4898352</v>
+        <v>8.793043600000001</v>
       </c>
       <c r="N30">
-        <v>109.1101648</v>
+        <v>108.8069564</v>
       </c>
       <c r="O30">
-        <v>17.457626368</v>
+        <v>17.409113024</v>
       </c>
       <c r="P30">
-        <v>91.652538432</v>
+        <v>91.397843376</v>
       </c>
       <c r="Q30">
-        <v>92.652538432</v>
+        <v>92.397843376</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08875880021026636</v>
+        <v>0.0892908824550676</v>
       </c>
       <c r="T30">
-        <v>0.591344054800771</v>
+        <v>0.5986683671788683</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>13.85185898543708</v>
+        <v>13.37420867559442</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07564960654309798</v>
+        <v>0.07556231693480418</v>
       </c>
       <c r="C31">
-        <v>452.4304524823219</v>
+        <v>446.6401124855451</v>
       </c>
       <c r="D31">
-        <v>488.842452482322</v>
+        <v>489.080112485545</v>
       </c>
       <c r="E31">
-        <v>-88.38800000000001</v>
+        <v>-82.36000000000001</v>
       </c>
       <c r="F31">
-        <v>174.812</v>
+        <v>180.84</v>
       </c>
       <c r="G31">
         <v>138.4</v>
@@ -3957,28 +3957,28 @@
         <v>117.6</v>
       </c>
       <c r="M31">
-        <v>8.793043599999999</v>
+        <v>9.096251999999998</v>
       </c>
       <c r="N31">
-        <v>108.8069564</v>
+        <v>108.503748</v>
       </c>
       <c r="O31">
-        <v>17.409113024</v>
+        <v>17.36059968</v>
       </c>
       <c r="P31">
-        <v>91.397843376</v>
+        <v>91.14314831999999</v>
       </c>
       <c r="Q31">
-        <v>92.397843376</v>
+        <v>92.14314831999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08929088245506758</v>
+        <v>0.08983816704972028</v>
       </c>
       <c r="T31">
-        <v>0.5986683671788682</v>
+        <v>0.6062019456249109</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.37420867559442</v>
+        <v>12.92840171974128</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07556231693480418</v>
+        <v>0.07586562732651042</v>
       </c>
       <c r="C32">
-        <v>446.6401124855451</v>
+        <v>439.7872930425662</v>
       </c>
       <c r="D32">
-        <v>489.080112485545</v>
+        <v>488.2552930425662</v>
       </c>
       <c r="E32">
-        <v>-82.36000000000001</v>
+        <v>-76.33199999999999</v>
       </c>
       <c r="F32">
-        <v>180.84</v>
+        <v>186.868</v>
       </c>
       <c r="G32">
         <v>138.4</v>
@@ -4039,45 +4039,45 @@
         <v>117.6</v>
       </c>
       <c r="M32">
-        <v>9.096251999999998</v>
+        <v>9.6797624</v>
       </c>
       <c r="N32">
-        <v>108.503748</v>
+        <v>107.9202376</v>
       </c>
       <c r="O32">
-        <v>17.36059968</v>
+        <v>17.267238016</v>
       </c>
       <c r="P32">
-        <v>91.14314831999999</v>
+        <v>90.65299958399999</v>
       </c>
       <c r="Q32">
-        <v>92.14314831999999</v>
+        <v>91.65299958399999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08983816704972028</v>
+        <v>0.09040131496595713</v>
       </c>
       <c r="T32">
-        <v>0.6062019456249109</v>
+        <v>0.6139538886635928</v>
       </c>
       <c r="U32">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V32">
         <v>0.16</v>
       </c>
       <c r="W32">
-        <v>0.042252</v>
+        <v>0.043512</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y32">
-        <v>12.92840171974128</v>
+        <v>12.14905853474255</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07586562732651042</v>
+        <v>0.07579093771821661</v>
       </c>
       <c r="C33">
-        <v>439.7872930425662</v>
+        <v>433.9621449678733</v>
       </c>
       <c r="D33">
-        <v>488.2552930425662</v>
+        <v>488.4581449678732</v>
       </c>
       <c r="E33">
-        <v>-76.33199999999999</v>
+        <v>-70.304</v>
       </c>
       <c r="F33">
-        <v>186.868</v>
+        <v>192.896</v>
       </c>
       <c r="G33">
         <v>138.4</v>
@@ -4121,28 +4121,28 @@
         <v>117.6</v>
       </c>
       <c r="M33">
-        <v>9.6797624</v>
+        <v>9.992012799999999</v>
       </c>
       <c r="N33">
-        <v>107.9202376</v>
+        <v>107.6079872</v>
       </c>
       <c r="O33">
-        <v>17.267238016</v>
+        <v>17.217277952</v>
       </c>
       <c r="P33">
-        <v>90.65299958399999</v>
+        <v>90.39070924799999</v>
       </c>
       <c r="Q33">
-        <v>91.65299958399999</v>
+        <v>91.39070924799999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09040131496595713</v>
+        <v>0.09098102605620093</v>
       </c>
       <c r="T33">
-        <v>0.6139538886635928</v>
+        <v>0.6219338300269416</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>12.14905853474255</v>
+        <v>11.76940045553184</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07579093771821661</v>
+        <v>0.07571624810992283</v>
       </c>
       <c r="C34">
-        <v>433.9621449678733</v>
+        <v>428.1371655181072</v>
       </c>
       <c r="D34">
-        <v>488.4581449678732</v>
+        <v>488.6611655181071</v>
       </c>
       <c r="E34">
-        <v>-70.304</v>
+        <v>-64.27599999999998</v>
       </c>
       <c r="F34">
-        <v>192.896</v>
+        <v>198.924</v>
       </c>
       <c r="G34">
         <v>138.4</v>
@@ -4203,28 +4203,28 @@
         <v>117.6</v>
       </c>
       <c r="M34">
-        <v>9.992012799999999</v>
+        <v>10.3042632</v>
       </c>
       <c r="N34">
-        <v>107.6079872</v>
+        <v>107.2957368</v>
       </c>
       <c r="O34">
-        <v>17.217277952</v>
+        <v>17.167317888</v>
       </c>
       <c r="P34">
-        <v>90.39070924799999</v>
+        <v>90.128418912</v>
       </c>
       <c r="Q34">
-        <v>91.39070924799999</v>
+        <v>91.128418912</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09098102605620093</v>
+        <v>0.09157804195510871</v>
       </c>
       <c r="T34">
-        <v>0.6219338300269416</v>
+        <v>0.6301519785951665</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>11.76940045553184</v>
+        <v>11.41275195687936</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07571624810992283</v>
+        <v>0.07564155850162904</v>
       </c>
       <c r="C35">
-        <v>428.1371655181072</v>
+        <v>422.3123549036148</v>
       </c>
       <c r="D35">
-        <v>488.6611655181071</v>
+        <v>488.8643549036148</v>
       </c>
       <c r="E35">
-        <v>-64.27599999999998</v>
+        <v>-58.24799999999999</v>
       </c>
       <c r="F35">
-        <v>198.924</v>
+        <v>204.952</v>
       </c>
       <c r="G35">
         <v>138.4</v>
@@ -4285,28 +4285,28 @@
         <v>117.6</v>
       </c>
       <c r="M35">
-        <v>10.3042632</v>
+        <v>10.6165136</v>
       </c>
       <c r="N35">
-        <v>107.2957368</v>
+        <v>106.9834864</v>
       </c>
       <c r="O35">
-        <v>17.167317888</v>
+        <v>17.117357824</v>
       </c>
       <c r="P35">
-        <v>90.128418912</v>
+        <v>89.86612857599999</v>
       </c>
       <c r="Q35">
-        <v>91.128418912</v>
+        <v>90.86612857599999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09157804195510871</v>
+        <v>0.0921931492448925</v>
       </c>
       <c r="T35">
-        <v>0.6301519785951665</v>
+        <v>0.6386191619684892</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.41275195687936</v>
+        <v>11.07708278167703</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07564155850162904</v>
+        <v>0.07556686889333525</v>
       </c>
       <c r="C36">
-        <v>422.3123549036148</v>
+        <v>416.4877133350934</v>
       </c>
       <c r="D36">
-        <v>488.8643549036148</v>
+        <v>489.0677133350935</v>
       </c>
       <c r="E36">
-        <v>-58.24799999999999</v>
+        <v>-52.21999999999997</v>
       </c>
       <c r="F36">
-        <v>204.952</v>
+        <v>210.98</v>
       </c>
       <c r="G36">
         <v>138.4</v>
@@ -4367,28 +4367,28 @@
         <v>117.6</v>
       </c>
       <c r="M36">
-        <v>10.6165136</v>
+        <v>10.928764</v>
       </c>
       <c r="N36">
-        <v>106.9834864</v>
+        <v>106.671236</v>
       </c>
       <c r="O36">
-        <v>17.117357824</v>
+        <v>17.06739776</v>
       </c>
       <c r="P36">
-        <v>89.86612857599999</v>
+        <v>89.60383823999999</v>
       </c>
       <c r="Q36">
-        <v>90.86612857599999</v>
+        <v>90.60383823999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0921931492448925</v>
+        <v>0.09282718291282348</v>
       </c>
       <c r="T36">
-        <v>0.6386191619684892</v>
+        <v>0.647346874060991</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.07708278167703</v>
+        <v>10.76059470220054</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07556686889333525</v>
+        <v>0.07549217928504147</v>
       </c>
       <c r="C37">
-        <v>416.4877133350934</v>
+        <v>410.6632410235904</v>
       </c>
       <c r="D37">
-        <v>489.0677133350935</v>
+        <v>489.2712410235904</v>
       </c>
       <c r="E37">
-        <v>-52.21999999999997</v>
+        <v>-46.19199999999998</v>
       </c>
       <c r="F37">
-        <v>210.98</v>
+        <v>217.008</v>
       </c>
       <c r="G37">
         <v>138.4</v>
@@ -4449,28 +4449,28 @@
         <v>117.6</v>
       </c>
       <c r="M37">
-        <v>10.928764</v>
+        <v>11.2410144</v>
       </c>
       <c r="N37">
-        <v>106.671236</v>
+        <v>106.3589856</v>
       </c>
       <c r="O37">
-        <v>17.06739776</v>
+        <v>17.017437696</v>
       </c>
       <c r="P37">
-        <v>89.60383823999999</v>
+        <v>89.341547904</v>
       </c>
       <c r="Q37">
-        <v>90.60383823999999</v>
+        <v>90.341547904</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09282718291282348</v>
+        <v>0.09348103013287731</v>
       </c>
       <c r="T37">
-        <v>0.647346874060991</v>
+        <v>0.6563473271563836</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>10.76059470220054</v>
+        <v>10.46168929380608</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07549217928504147</v>
+        <v>0.07541748967674769</v>
       </c>
       <c r="C38">
-        <v>410.6632410235905</v>
+        <v>404.8389381805051</v>
       </c>
       <c r="D38">
-        <v>489.2712410235904</v>
+        <v>489.4749381805051</v>
       </c>
       <c r="E38">
-        <v>-46.19200000000001</v>
+        <v>-40.16400000000002</v>
       </c>
       <c r="F38">
-        <v>217.008</v>
+        <v>223.036</v>
       </c>
       <c r="G38">
         <v>138.4</v>
@@ -4531,28 +4531,28 @@
         <v>117.6</v>
       </c>
       <c r="M38">
-        <v>11.2410144</v>
+        <v>11.5532648</v>
       </c>
       <c r="N38">
-        <v>106.3589856</v>
+        <v>106.0467352</v>
       </c>
       <c r="O38">
-        <v>17.017437696</v>
+        <v>16.967477632</v>
       </c>
       <c r="P38">
-        <v>89.341547904</v>
+        <v>89.079257568</v>
       </c>
       <c r="Q38">
-        <v>90.341547904</v>
+        <v>90.079257568</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09348103013287729</v>
+        <v>0.09415563440753601</v>
       </c>
       <c r="T38">
-        <v>0.6563473271563834</v>
+        <v>0.665633508921471</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.46168929380608</v>
+        <v>10.17894093451403</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07541748967674769</v>
+        <v>0.07534280006845388</v>
       </c>
       <c r="C39">
-        <v>404.8389381805051</v>
+        <v>399.0148050175887</v>
       </c>
       <c r="D39">
-        <v>489.4749381805051</v>
+        <v>489.6788050175887</v>
       </c>
       <c r="E39">
-        <v>-40.16400000000002</v>
+        <v>-34.136</v>
       </c>
       <c r="F39">
-        <v>223.036</v>
+        <v>229.064</v>
       </c>
       <c r="G39">
         <v>138.4</v>
@@ -4613,28 +4613,28 @@
         <v>117.6</v>
       </c>
       <c r="M39">
-        <v>11.5532648</v>
+        <v>11.8655152</v>
       </c>
       <c r="N39">
-        <v>106.0467352</v>
+        <v>105.7344848</v>
       </c>
       <c r="O39">
-        <v>16.967477632</v>
+        <v>16.917517568</v>
       </c>
       <c r="P39">
-        <v>89.079257568</v>
+        <v>88.816967232</v>
       </c>
       <c r="Q39">
-        <v>90.079257568</v>
+        <v>89.816967232</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09415563440753601</v>
+        <v>0.09485200011040949</v>
       </c>
       <c r="T39">
-        <v>0.665633508921471</v>
+        <v>0.675219244937045</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.17894093451403</v>
+        <v>9.911074067816289</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07534280006845388</v>
+        <v>0.07582503046016011</v>
       </c>
       <c r="C40">
-        <v>399.0148050175887</v>
+        <v>391.6735304806272</v>
       </c>
       <c r="D40">
-        <v>489.6788050175887</v>
+        <v>488.3655304806271</v>
       </c>
       <c r="E40">
-        <v>-34.136</v>
+        <v>-28.108</v>
       </c>
       <c r="F40">
-        <v>229.064</v>
+        <v>235.092</v>
       </c>
       <c r="G40">
         <v>138.4</v>
@@ -4695,45 +4695,45 @@
         <v>117.6</v>
       </c>
       <c r="M40">
-        <v>11.8655152</v>
+        <v>12.577422</v>
       </c>
       <c r="N40">
-        <v>105.7344848</v>
+        <v>105.022578</v>
       </c>
       <c r="O40">
-        <v>16.917517568</v>
+        <v>16.80361248</v>
       </c>
       <c r="P40">
-        <v>88.816967232</v>
+        <v>88.21896552</v>
       </c>
       <c r="Q40">
-        <v>89.816967232</v>
+        <v>89.21896552</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09485200011040949</v>
+        <v>0.0955711974756723</v>
       </c>
       <c r="T40">
-        <v>0.675219244937045</v>
+        <v>0.6851192673793594</v>
       </c>
       <c r="U40">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V40">
         <v>0.16</v>
       </c>
       <c r="W40">
-        <v>0.043512</v>
+        <v>0.04494</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>9.911074067816289</v>
+        <v>9.350087800186715</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07582503046016011</v>
+        <v>0.07576462085186632</v>
       </c>
       <c r="C41">
-        <v>391.6735304806272</v>
+        <v>385.8096599613141</v>
       </c>
       <c r="D41">
-        <v>488.3655304806271</v>
+        <v>488.5296599613141</v>
       </c>
       <c r="E41">
-        <v>-28.108</v>
+        <v>-22.07999999999998</v>
       </c>
       <c r="F41">
-        <v>235.092</v>
+        <v>241.12</v>
       </c>
       <c r="G41">
         <v>138.4</v>
@@ -4777,28 +4777,28 @@
         <v>117.6</v>
       </c>
       <c r="M41">
-        <v>12.577422</v>
+        <v>12.89992</v>
       </c>
       <c r="N41">
-        <v>105.022578</v>
+        <v>104.70008</v>
       </c>
       <c r="O41">
-        <v>16.80361248</v>
+        <v>16.7520128</v>
       </c>
       <c r="P41">
-        <v>88.21896552</v>
+        <v>87.9480672</v>
       </c>
       <c r="Q41">
-        <v>89.21896552</v>
+        <v>88.9480672</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.0955711974756723</v>
+        <v>0.09631436808644386</v>
       </c>
       <c r="T41">
-        <v>0.6851192673793594</v>
+        <v>0.6953492905697509</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>9.350087800186715</v>
+        <v>9.116335605182048</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07576462085186632</v>
+        <v>0.07570421124357252</v>
       </c>
       <c r="C42">
-        <v>385.8096599613141</v>
+        <v>379.9458998000883</v>
       </c>
       <c r="D42">
-        <v>488.5296599613141</v>
+        <v>488.6938998000883</v>
       </c>
       <c r="E42">
-        <v>-22.07999999999998</v>
+        <v>-16.05199999999999</v>
       </c>
       <c r="F42">
-        <v>241.12</v>
+        <v>247.148</v>
       </c>
       <c r="G42">
         <v>138.4</v>
@@ -4859,28 +4859,28 @@
         <v>117.6</v>
       </c>
       <c r="M42">
-        <v>12.89992</v>
+        <v>13.222418</v>
       </c>
       <c r="N42">
-        <v>104.70008</v>
+        <v>104.377582</v>
       </c>
       <c r="O42">
-        <v>16.7520128</v>
+        <v>16.70041312</v>
       </c>
       <c r="P42">
-        <v>87.9480672</v>
+        <v>87.67716887999998</v>
       </c>
       <c r="Q42">
-        <v>88.9480672</v>
+        <v>88.67716887999998</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09631436808644386</v>
+        <v>0.09708273092130937</v>
       </c>
       <c r="T42">
-        <v>0.6953492905697509</v>
+        <v>0.7059260942072743</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.116335605182048</v>
+        <v>8.893985956275168</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07570421124357252</v>
+        <v>0.07564380163527873</v>
       </c>
       <c r="C43">
-        <v>379.9458998000883</v>
+        <v>374.0822501082919</v>
       </c>
       <c r="D43">
-        <v>488.6938998000883</v>
+        <v>488.8582501082919</v>
       </c>
       <c r="E43">
-        <v>-16.05199999999999</v>
+        <v>-10.02399999999997</v>
       </c>
       <c r="F43">
-        <v>247.148</v>
+        <v>253.176</v>
       </c>
       <c r="G43">
         <v>138.4</v>
@@ -4941,28 +4941,28 @@
         <v>117.6</v>
       </c>
       <c r="M43">
-        <v>13.222418</v>
+        <v>13.544916</v>
       </c>
       <c r="N43">
-        <v>104.377582</v>
+        <v>104.055084</v>
       </c>
       <c r="O43">
-        <v>16.70041312</v>
+        <v>16.64881344</v>
       </c>
       <c r="P43">
-        <v>87.67716887999998</v>
+        <v>87.40627056</v>
       </c>
       <c r="Q43">
-        <v>88.67716887999998</v>
+        <v>88.40627056</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09708273092130937</v>
+        <v>0.09787758902634265</v>
       </c>
       <c r="T43">
-        <v>0.7059260942072743</v>
+        <v>0.7168676152116088</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.893985956275168</v>
+        <v>8.682224385887665</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07564380163527874</v>
+        <v>0.07558339202698494</v>
       </c>
       <c r="C44">
-        <v>374.082250108292</v>
+        <v>368.2187109974168</v>
       </c>
       <c r="D44">
-        <v>488.8582501082919</v>
+        <v>489.0227109974168</v>
       </c>
       <c r="E44">
-        <v>-10.02400000000003</v>
+        <v>-3.996000000000038</v>
       </c>
       <c r="F44">
-        <v>253.176</v>
+        <v>259.204</v>
       </c>
       <c r="G44">
         <v>138.4</v>
@@ -5023,28 +5023,28 @@
         <v>117.6</v>
       </c>
       <c r="M44">
-        <v>13.544916</v>
+        <v>13.867414</v>
       </c>
       <c r="N44">
-        <v>104.055084</v>
+        <v>103.732586</v>
       </c>
       <c r="O44">
-        <v>16.64881344</v>
+        <v>16.59721376</v>
       </c>
       <c r="P44">
-        <v>87.40627056</v>
+        <v>87.13537224</v>
       </c>
       <c r="Q44">
-        <v>88.40627056</v>
+        <v>88.13537224</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09787758902634265</v>
+        <v>0.09870033688944727</v>
       </c>
       <c r="T44">
-        <v>0.7168676152116088</v>
+        <v>0.7281930492336391</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.682224385887665</v>
+        <v>8.480312190867023</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07558339202698494</v>
+        <v>0.07552298241869117</v>
       </c>
       <c r="C45">
-        <v>368.2187109974168</v>
+        <v>362.3552825791047</v>
       </c>
       <c r="D45">
-        <v>489.0227109974168</v>
+        <v>489.1872825791047</v>
       </c>
       <c r="E45">
-        <v>-3.996000000000038</v>
+        <v>2.031999999999982</v>
       </c>
       <c r="F45">
-        <v>259.204</v>
+        <v>265.232</v>
       </c>
       <c r="G45">
         <v>138.4</v>
@@ -5105,28 +5105,28 @@
         <v>117.6</v>
       </c>
       <c r="M45">
-        <v>13.867414</v>
+        <v>14.189912</v>
       </c>
       <c r="N45">
-        <v>103.732586</v>
+        <v>103.410088</v>
       </c>
       <c r="O45">
-        <v>16.59721376</v>
+        <v>16.54561408</v>
       </c>
       <c r="P45">
-        <v>87.13537224</v>
+        <v>86.86447391999999</v>
       </c>
       <c r="Q45">
-        <v>88.13537224</v>
+        <v>87.86447391999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09870033688944727</v>
+        <v>0.09955246860480564</v>
       </c>
       <c r="T45">
-        <v>0.7281930492336391</v>
+        <v>0.7399229630421708</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.480312190867023</v>
+        <v>8.287577822892771</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07552298241869117</v>
+        <v>0.07546257281039738</v>
       </c>
       <c r="C46">
-        <v>362.3552825791047</v>
+        <v>356.491964965148</v>
       </c>
       <c r="D46">
-        <v>489.1872825791047</v>
+        <v>489.3519649651479</v>
       </c>
       <c r="E46">
-        <v>2.031999999999982</v>
+        <v>8.060000000000002</v>
       </c>
       <c r="F46">
-        <v>265.232</v>
+        <v>271.26</v>
       </c>
       <c r="G46">
         <v>138.4</v>
@@ -5187,28 +5187,28 @@
         <v>117.6</v>
       </c>
       <c r="M46">
-        <v>14.189912</v>
+        <v>14.51241</v>
       </c>
       <c r="N46">
-        <v>103.410088</v>
+        <v>103.08759</v>
       </c>
       <c r="O46">
-        <v>16.54561408</v>
+        <v>16.4940144</v>
       </c>
       <c r="P46">
-        <v>86.86447391999999</v>
+        <v>86.59357559999999</v>
       </c>
       <c r="Q46">
-        <v>87.86447391999999</v>
+        <v>87.59357559999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09955246860480564</v>
+        <v>0.1004355869279952</v>
       </c>
       <c r="T46">
-        <v>0.7399229630421708</v>
+        <v>0.7520794191710125</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.287577822892771</v>
+        <v>8.103409426828486</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07546257281039738</v>
+        <v>0.07540216320210358</v>
       </c>
       <c r="C47">
-        <v>356.491964965148</v>
+        <v>350.6287582674894</v>
       </c>
       <c r="D47">
-        <v>489.3519649651479</v>
+        <v>489.5167582674894</v>
       </c>
       <c r="E47">
-        <v>8.060000000000002</v>
+        <v>14.08800000000002</v>
       </c>
       <c r="F47">
-        <v>271.26</v>
+        <v>277.288</v>
       </c>
       <c r="G47">
         <v>138.4</v>
@@ -5269,28 +5269,28 @@
         <v>117.6</v>
       </c>
       <c r="M47">
-        <v>14.51241</v>
+        <v>14.834908</v>
       </c>
       <c r="N47">
-        <v>103.08759</v>
+        <v>102.765092</v>
       </c>
       <c r="O47">
-        <v>16.4940144</v>
+        <v>16.44241472</v>
       </c>
       <c r="P47">
-        <v>86.59357559999999</v>
+        <v>86.32267727999999</v>
       </c>
       <c r="Q47">
-        <v>87.59357559999999</v>
+        <v>87.32267727999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1004355869279952</v>
+        <v>0.1013514133372289</v>
       </c>
       <c r="T47">
-        <v>0.7520794191710125</v>
+        <v>0.7646861144157374</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.103409426828486</v>
+        <v>7.927248352332215</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07540216320210358</v>
+        <v>0.07534175359380979</v>
       </c>
       <c r="C48">
-        <v>350.6287582674894</v>
+        <v>344.7656625982228</v>
       </c>
       <c r="D48">
-        <v>489.5167582674894</v>
+        <v>489.6816625982228</v>
       </c>
       <c r="E48">
-        <v>14.08800000000002</v>
+        <v>20.11599999999999</v>
       </c>
       <c r="F48">
-        <v>277.288</v>
+        <v>283.316</v>
       </c>
       <c r="G48">
         <v>138.4</v>
@@ -5351,28 +5351,28 @@
         <v>117.6</v>
       </c>
       <c r="M48">
-        <v>14.834908</v>
+        <v>15.157406</v>
       </c>
       <c r="N48">
-        <v>102.765092</v>
+        <v>102.442594</v>
       </c>
       <c r="O48">
-        <v>16.44241472</v>
+        <v>16.39081504</v>
       </c>
       <c r="P48">
-        <v>86.32267727999999</v>
+        <v>86.05177896000001</v>
       </c>
       <c r="Q48">
-        <v>87.32267727999999</v>
+        <v>87.05177896000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1013514133372289</v>
+        <v>0.1023017992336034</v>
       </c>
       <c r="T48">
-        <v>0.7646861144157374</v>
+        <v>0.7777685340093198</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.927248352332215</v>
+        <v>7.758583493771956</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07534175359380979</v>
+        <v>0.07560390398551602</v>
       </c>
       <c r="C49">
-        <v>344.7656625982228</v>
+        <v>338.0228562339052</v>
       </c>
       <c r="D49">
-        <v>489.6816625982228</v>
+        <v>488.9668562339052</v>
       </c>
       <c r="E49">
-        <v>20.11599999999999</v>
+        <v>26.14400000000001</v>
       </c>
       <c r="F49">
-        <v>283.316</v>
+        <v>289.344</v>
       </c>
       <c r="G49">
         <v>138.4</v>
@@ -5433,45 +5433,45 @@
         <v>117.6</v>
       </c>
       <c r="M49">
-        <v>15.157406</v>
+        <v>15.7113792</v>
       </c>
       <c r="N49">
-        <v>102.442594</v>
+        <v>101.8886208</v>
       </c>
       <c r="O49">
-        <v>16.39081504</v>
+        <v>16.302179328</v>
       </c>
       <c r="P49">
-        <v>86.05177896000001</v>
+        <v>85.58644147199999</v>
       </c>
       <c r="Q49">
-        <v>87.05177896000001</v>
+        <v>86.58644147199999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1023017992336034</v>
+        <v>0.1032887384336846</v>
       </c>
       <c r="T49">
-        <v>0.7777685340093198</v>
+        <v>0.7913541235872709</v>
       </c>
       <c r="U49">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V49">
         <v>0.16</v>
       </c>
       <c r="W49">
-        <v>0.04494</v>
+        <v>0.045612</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y49">
-        <v>7.758583493771956</v>
+        <v>7.485020793082252</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.075603903985516</v>
+        <v>0.07555021437722222</v>
       </c>
       <c r="C50">
-        <v>338.0228562339052</v>
+        <v>332.1410818880101</v>
       </c>
       <c r="D50">
-        <v>488.9668562339052</v>
+        <v>489.1130818880101</v>
       </c>
       <c r="E50">
-        <v>26.14400000000001</v>
+        <v>32.17199999999997</v>
       </c>
       <c r="F50">
-        <v>289.344</v>
+        <v>295.372</v>
       </c>
       <c r="G50">
         <v>138.4</v>
@@ -5515,28 +5515,28 @@
         <v>117.6</v>
       </c>
       <c r="M50">
-        <v>15.7113792</v>
+        <v>16.0386996</v>
       </c>
       <c r="N50">
-        <v>101.8886208</v>
+        <v>101.5613004</v>
       </c>
       <c r="O50">
-        <v>16.302179328</v>
+        <v>16.249808064</v>
       </c>
       <c r="P50">
-        <v>85.58644147199999</v>
+        <v>85.31149233599999</v>
       </c>
       <c r="Q50">
-        <v>86.58644147199999</v>
+        <v>86.31149233599999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1032887384336846</v>
+        <v>0.1043143811318083</v>
       </c>
       <c r="T50">
-        <v>0.7913541235872708</v>
+        <v>0.8054724813839649</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.485020793082252</v>
+        <v>7.332265266692819</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07555021437722222</v>
+        <v>0.07549652476892843</v>
       </c>
       <c r="C51">
-        <v>332.1410818880101</v>
+        <v>326.2593950259098</v>
       </c>
       <c r="D51">
-        <v>489.1130818880101</v>
+        <v>489.2593950259098</v>
       </c>
       <c r="E51">
-        <v>32.17199999999997</v>
+        <v>38.19999999999999</v>
       </c>
       <c r="F51">
-        <v>295.372</v>
+        <v>301.4</v>
       </c>
       <c r="G51">
         <v>138.4</v>
@@ -5597,28 +5597,28 @@
         <v>117.6</v>
       </c>
       <c r="M51">
-        <v>16.0386996</v>
+        <v>16.36602</v>
       </c>
       <c r="N51">
-        <v>101.5613004</v>
+        <v>101.23398</v>
       </c>
       <c r="O51">
-        <v>16.249808064</v>
+        <v>16.1974368</v>
       </c>
       <c r="P51">
-        <v>85.31149233599999</v>
+        <v>85.0365432</v>
       </c>
       <c r="Q51">
-        <v>86.31149233599999</v>
+        <v>86.0365432</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1043143811318083</v>
+        <v>0.1053810495378568</v>
       </c>
       <c r="T51">
-        <v>0.8054724813839649</v>
+        <v>0.8201555734925267</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.332265266692819</v>
+        <v>7.185619961358962</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07549652476892843</v>
+        <v>0.07544283516063464</v>
       </c>
       <c r="C52">
-        <v>326.2593950259098</v>
+        <v>320.3777957261378</v>
       </c>
       <c r="D52">
-        <v>489.2593950259098</v>
+        <v>489.4057957261378</v>
       </c>
       <c r="E52">
-        <v>38.19999999999999</v>
+        <v>44.22800000000001</v>
       </c>
       <c r="F52">
-        <v>301.4</v>
+        <v>307.428</v>
       </c>
       <c r="G52">
         <v>138.4</v>
@@ -5679,28 +5679,28 @@
         <v>117.6</v>
       </c>
       <c r="M52">
-        <v>16.36602</v>
+        <v>16.6933404</v>
       </c>
       <c r="N52">
-        <v>101.23398</v>
+        <v>100.9066596</v>
       </c>
       <c r="O52">
-        <v>16.1974368</v>
+        <v>16.145065536</v>
       </c>
       <c r="P52">
-        <v>85.0365432</v>
+        <v>84.76159406399999</v>
       </c>
       <c r="Q52">
-        <v>86.0365432</v>
+        <v>85.76159406399999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1053810495378568</v>
+        <v>0.1064912554298666</v>
       </c>
       <c r="T52">
-        <v>0.8201555734925267</v>
+        <v>0.8354379754830706</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.185619961358962</v>
+        <v>7.044725452312708</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07544283516063464</v>
+        <v>0.07538914555234086</v>
       </c>
       <c r="C53">
-        <v>320.3777957261378</v>
+        <v>314.4962840673211</v>
       </c>
       <c r="D53">
-        <v>489.4057957261378</v>
+        <v>489.5522840673211</v>
       </c>
       <c r="E53">
-        <v>44.22800000000001</v>
+        <v>50.25599999999997</v>
       </c>
       <c r="F53">
-        <v>307.428</v>
+        <v>313.456</v>
       </c>
       <c r="G53">
         <v>138.4</v>
@@ -5761,28 +5761,28 @@
         <v>117.6</v>
       </c>
       <c r="M53">
-        <v>16.6933404</v>
+        <v>17.0206608</v>
       </c>
       <c r="N53">
-        <v>100.9066596</v>
+        <v>100.5793392</v>
       </c>
       <c r="O53">
-        <v>16.145065536</v>
+        <v>16.092694272</v>
       </c>
       <c r="P53">
-        <v>84.76159406399999</v>
+        <v>84.48664492799999</v>
       </c>
       <c r="Q53">
-        <v>85.76159406399999</v>
+        <v>85.48664492799999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1064912554298666</v>
+        <v>0.1076477199007101</v>
       </c>
       <c r="T53">
-        <v>0.8354379754830706</v>
+        <v>0.8513571442232207</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.044725452312708</v>
+        <v>6.909249962845156</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07538914555234086</v>
+        <v>0.07533545594404706</v>
       </c>
       <c r="C54">
-        <v>314.4962840673211</v>
+        <v>308.6148601281807</v>
       </c>
       <c r="D54">
-        <v>489.5522840673211</v>
+        <v>489.6988601281807</v>
       </c>
       <c r="E54">
-        <v>50.25599999999997</v>
+        <v>56.28399999999999</v>
       </c>
       <c r="F54">
-        <v>313.456</v>
+        <v>319.484</v>
       </c>
       <c r="G54">
         <v>138.4</v>
@@ -5843,28 +5843,28 @@
         <v>117.6</v>
       </c>
       <c r="M54">
-        <v>17.0206608</v>
+        <v>17.3479812</v>
       </c>
       <c r="N54">
-        <v>100.5793392</v>
+        <v>100.2520188</v>
       </c>
       <c r="O54">
-        <v>16.092694272</v>
+        <v>16.040323008</v>
       </c>
       <c r="P54">
-        <v>84.48664492799999</v>
+        <v>84.211695792</v>
       </c>
       <c r="Q54">
-        <v>85.48664492799999</v>
+        <v>85.211695792</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1076477199007101</v>
+        <v>0.108853395625632</v>
       </c>
       <c r="T54">
-        <v>0.8513571442232207</v>
+        <v>0.8679537243991217</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.909249962845156</v>
+        <v>6.778886755999021</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07533545594404706</v>
+        <v>0.07528176633575327</v>
       </c>
       <c r="C55">
-        <v>308.6148601281807</v>
+        <v>302.7335239875327</v>
       </c>
       <c r="D55">
-        <v>489.6988601281807</v>
+        <v>489.8455239875327</v>
       </c>
       <c r="E55">
-        <v>56.28399999999999</v>
+        <v>62.31200000000001</v>
       </c>
       <c r="F55">
-        <v>319.484</v>
+        <v>325.512</v>
       </c>
       <c r="G55">
         <v>138.4</v>
@@ -5925,28 +5925,28 @@
         <v>117.6</v>
       </c>
       <c r="M55">
-        <v>17.3479812</v>
+        <v>17.6753016</v>
       </c>
       <c r="N55">
-        <v>100.2520188</v>
+        <v>99.9246984</v>
       </c>
       <c r="O55">
-        <v>16.040323008</v>
+        <v>15.987951744</v>
       </c>
       <c r="P55">
-        <v>84.211695792</v>
+        <v>83.936746656</v>
       </c>
       <c r="Q55">
-        <v>85.211695792</v>
+        <v>84.936746656</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.108853395625632</v>
+        <v>0.1101114920342462</v>
       </c>
       <c r="T55">
-        <v>0.8679537243991217</v>
+        <v>0.8852718950174532</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.778886755999021</v>
+        <v>6.653351816073113</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07528176633575327</v>
+        <v>0.07522807672745949</v>
       </c>
       <c r="C56">
-        <v>302.7335239875327</v>
+        <v>296.852275724287</v>
       </c>
       <c r="D56">
-        <v>489.8455239875327</v>
+        <v>489.992275724287</v>
       </c>
       <c r="E56">
-        <v>62.31200000000001</v>
+        <v>68.34000000000003</v>
       </c>
       <c r="F56">
-        <v>325.512</v>
+        <v>331.54</v>
       </c>
       <c r="G56">
         <v>138.4</v>
@@ -6007,28 +6007,28 @@
         <v>117.6</v>
       </c>
       <c r="M56">
-        <v>17.6753016</v>
+        <v>18.002622</v>
       </c>
       <c r="N56">
-        <v>99.9246984</v>
+        <v>99.59737799999999</v>
       </c>
       <c r="O56">
-        <v>15.987951744</v>
+        <v>15.93558048</v>
       </c>
       <c r="P56">
-        <v>83.936746656</v>
+        <v>83.66179751999999</v>
       </c>
       <c r="Q56">
-        <v>84.936746656</v>
+        <v>84.66179751999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1101114920342462</v>
+        <v>0.1114255038387989</v>
       </c>
       <c r="T56">
-        <v>0.8852718950174532</v>
+        <v>0.9033597621077106</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.653351816073113</v>
+        <v>6.532381783053601</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07522807672745949</v>
+        <v>0.0751743871191657</v>
       </c>
       <c r="C57">
-        <v>296.852275724287</v>
+        <v>290.9711154174482</v>
       </c>
       <c r="D57">
-        <v>489.992275724287</v>
+        <v>490.1391154174482</v>
       </c>
       <c r="E57">
-        <v>68.34000000000003</v>
+        <v>74.36799999999999</v>
       </c>
       <c r="F57">
-        <v>331.54</v>
+        <v>337.568</v>
       </c>
       <c r="G57">
         <v>138.4</v>
@@ -6089,28 +6089,28 @@
         <v>117.6</v>
       </c>
       <c r="M57">
-        <v>18.002622</v>
+        <v>18.3299424</v>
       </c>
       <c r="N57">
-        <v>99.59737799999999</v>
+        <v>99.2700576</v>
       </c>
       <c r="O57">
-        <v>15.93558048</v>
+        <v>15.883209216</v>
       </c>
       <c r="P57">
-        <v>83.66179751999999</v>
+        <v>83.386848384</v>
       </c>
       <c r="Q57">
-        <v>84.66179751999999</v>
+        <v>84.386848384</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1114255038387989</v>
+        <v>0.1127992434526493</v>
       </c>
       <c r="T57">
-        <v>0.9033597621077106</v>
+        <v>0.9222698049747979</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.532381783053601</v>
+        <v>6.415732108356216</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0751743871191657</v>
+        <v>0.07512069751087191</v>
       </c>
       <c r="C58">
-        <v>290.9711154174482</v>
+        <v>285.0900431461156</v>
       </c>
       <c r="D58">
-        <v>490.1391154174482</v>
+        <v>490.2860431461156</v>
       </c>
       <c r="E58">
-        <v>74.36799999999999</v>
+        <v>80.39600000000002</v>
       </c>
       <c r="F58">
-        <v>337.568</v>
+        <v>343.596</v>
       </c>
       <c r="G58">
         <v>138.4</v>
@@ -6171,28 +6171,28 @@
         <v>117.6</v>
       </c>
       <c r="M58">
-        <v>18.3299424</v>
+        <v>18.6572628</v>
       </c>
       <c r="N58">
-        <v>99.2700576</v>
+        <v>98.9427372</v>
       </c>
       <c r="O58">
-        <v>15.883209216</v>
+        <v>15.830837952</v>
       </c>
       <c r="P58">
-        <v>83.386848384</v>
+        <v>83.111899248</v>
       </c>
       <c r="Q58">
-        <v>84.386848384</v>
+        <v>84.111899248</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1127992434526493</v>
+        <v>0.1142368779322603</v>
       </c>
       <c r="T58">
-        <v>0.9222698049747979</v>
+        <v>0.942059384719424</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.415732108356216</v>
+        <v>6.303175404700843</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07512069751087191</v>
+        <v>0.07506700790257811</v>
       </c>
       <c r="C59">
-        <v>285.0900431461156</v>
+        <v>279.2090589894837</v>
       </c>
       <c r="D59">
-        <v>490.2860431461156</v>
+        <v>490.4330589894837</v>
       </c>
       <c r="E59">
-        <v>80.39600000000002</v>
+        <v>86.42400000000004</v>
       </c>
       <c r="F59">
-        <v>343.596</v>
+        <v>349.624</v>
       </c>
       <c r="G59">
         <v>138.4</v>
@@ -6253,28 +6253,28 @@
         <v>117.6</v>
       </c>
       <c r="M59">
-        <v>18.6572628</v>
+        <v>18.9845832</v>
       </c>
       <c r="N59">
-        <v>98.9427372</v>
+        <v>98.61541679999999</v>
       </c>
       <c r="O59">
-        <v>15.830837952</v>
+        <v>15.778466688</v>
       </c>
       <c r="P59">
-        <v>83.111899248</v>
+        <v>82.836950112</v>
       </c>
       <c r="Q59">
-        <v>84.111899248</v>
+        <v>83.836950112</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1142368779322603</v>
+        <v>0.1157429711966146</v>
       </c>
       <c r="T59">
-        <v>0.942059384719424</v>
+        <v>0.9627913254042705</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.303175404700843</v>
+        <v>6.194499966688759</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07506700790257811</v>
+        <v>0.07550891829428433</v>
       </c>
       <c r="C60">
-        <v>279.2090589894837</v>
+        <v>271.9736128315748</v>
       </c>
       <c r="D60">
-        <v>490.4330589894837</v>
+        <v>489.2256128315747</v>
       </c>
       <c r="E60">
-        <v>86.42399999999998</v>
+        <v>92.45199999999994</v>
       </c>
       <c r="F60">
-        <v>349.624</v>
+        <v>355.6519999999999</v>
       </c>
       <c r="G60">
         <v>138.4</v>
@@ -6335,45 +6335,45 @@
         <v>117.6</v>
       </c>
       <c r="M60">
-        <v>18.9845832</v>
+        <v>19.6675556</v>
       </c>
       <c r="N60">
-        <v>98.61541679999999</v>
+        <v>97.93244439999999</v>
       </c>
       <c r="O60">
-        <v>15.778466688</v>
+        <v>15.669191104</v>
       </c>
       <c r="P60">
-        <v>82.836950112</v>
+        <v>82.26325329599999</v>
       </c>
       <c r="Q60">
-        <v>83.836950112</v>
+        <v>83.26325329599999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1157429711966146</v>
+        <v>0.1173225324250837</v>
       </c>
       <c r="T60">
-        <v>0.9627913254042704</v>
+        <v>0.9845345802688654</v>
       </c>
       <c r="U60">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V60">
         <v>0.16</v>
       </c>
       <c r="W60">
-        <v>0.045612</v>
+        <v>0.046452</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>6.19449996668876</v>
+        <v>5.979390748487321</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07550891829428433</v>
+        <v>0.07546362868599055</v>
       </c>
       <c r="C61">
-        <v>271.9736128315748</v>
+        <v>266.0690855949507</v>
       </c>
       <c r="D61">
-        <v>489.2256128315747</v>
+        <v>489.3490855949506</v>
       </c>
       <c r="E61">
-        <v>92.45199999999994</v>
+        <v>98.47999999999996</v>
       </c>
       <c r="F61">
-        <v>355.6519999999999</v>
+        <v>361.6799999999999</v>
       </c>
       <c r="G61">
         <v>138.4</v>
@@ -6417,28 +6417,28 @@
         <v>117.6</v>
       </c>
       <c r="M61">
-        <v>19.6675556</v>
+        <v>20.000904</v>
       </c>
       <c r="N61">
-        <v>97.93244439999999</v>
+        <v>97.599096</v>
       </c>
       <c r="O61">
-        <v>15.669191104</v>
+        <v>15.61585536</v>
       </c>
       <c r="P61">
-        <v>82.26325329599999</v>
+        <v>81.98324064000001</v>
       </c>
       <c r="Q61">
-        <v>83.26325329599999</v>
+        <v>82.98324064000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1173225324250837</v>
+        <v>0.1189810717149763</v>
       </c>
       <c r="T61">
-        <v>0.9845345802688654</v>
+        <v>1.00736499787669</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.979390748487321</v>
+        <v>5.879734236012533</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07546362868599055</v>
+        <v>0.07541833907769675</v>
       </c>
       <c r="C62">
-        <v>266.0690855949507</v>
+        <v>260.1646206991837</v>
       </c>
       <c r="D62">
-        <v>489.3490855949506</v>
+        <v>489.4726206991837</v>
       </c>
       <c r="E62">
-        <v>98.47999999999996</v>
+        <v>104.508</v>
       </c>
       <c r="F62">
-        <v>361.6799999999999</v>
+        <v>367.708</v>
       </c>
       <c r="G62">
         <v>138.4</v>
@@ -6499,28 +6499,28 @@
         <v>117.6</v>
       </c>
       <c r="M62">
-        <v>20.000904</v>
+        <v>20.3342524</v>
       </c>
       <c r="N62">
-        <v>97.599096</v>
+        <v>97.2657476</v>
       </c>
       <c r="O62">
-        <v>15.61585536</v>
+        <v>15.562519616</v>
       </c>
       <c r="P62">
-        <v>81.98324064000001</v>
+        <v>81.70322798399999</v>
       </c>
       <c r="Q62">
-        <v>82.98324064000001</v>
+        <v>82.70322798399999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1189810717149763</v>
+        <v>0.1207246643017865</v>
       </c>
       <c r="T62">
-        <v>1.00736499787669</v>
+        <v>1.03136620613107</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.879734236012533</v>
+        <v>5.783345150176261</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07541833907769675</v>
+        <v>0.07537304946940296</v>
       </c>
       <c r="C63">
-        <v>260.1646206991837</v>
+        <v>254.2602181914991</v>
       </c>
       <c r="D63">
-        <v>489.4726206991837</v>
+        <v>489.5962181914991</v>
       </c>
       <c r="E63">
-        <v>104.508</v>
+        <v>110.536</v>
       </c>
       <c r="F63">
-        <v>367.708</v>
+        <v>373.736</v>
       </c>
       <c r="G63">
         <v>138.4</v>
@@ -6581,28 +6581,28 @@
         <v>117.6</v>
       </c>
       <c r="M63">
-        <v>20.3342524</v>
+        <v>20.6676008</v>
       </c>
       <c r="N63">
-        <v>97.2657476</v>
+        <v>96.93239919999999</v>
       </c>
       <c r="O63">
-        <v>15.562519616</v>
+        <v>15.509183872</v>
       </c>
       <c r="P63">
-        <v>81.70322798399999</v>
+        <v>81.423215328</v>
       </c>
       <c r="Q63">
-        <v>82.70322798399999</v>
+        <v>82.423215328</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1207246643017865</v>
+        <v>0.1225600249194815</v>
       </c>
       <c r="T63">
-        <v>1.03136620613107</v>
+        <v>1.056630635872523</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.783345150176261</v>
+        <v>5.690065389689547</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07537304946940296</v>
+        <v>0.07532775986110918</v>
       </c>
       <c r="C64">
-        <v>254.2602181914991</v>
+        <v>248.35587811917</v>
       </c>
       <c r="D64">
-        <v>489.5962181914991</v>
+        <v>489.7198781191699</v>
       </c>
       <c r="E64">
-        <v>110.536</v>
+        <v>116.564</v>
       </c>
       <c r="F64">
-        <v>373.736</v>
+        <v>379.764</v>
       </c>
       <c r="G64">
         <v>138.4</v>
@@ -6663,28 +6663,28 @@
         <v>117.6</v>
       </c>
       <c r="M64">
-        <v>20.6676008</v>
+        <v>21.0009492</v>
       </c>
       <c r="N64">
-        <v>96.93239919999999</v>
+        <v>96.5990508</v>
       </c>
       <c r="O64">
-        <v>15.509183872</v>
+        <v>15.455848128</v>
       </c>
       <c r="P64">
-        <v>81.423215328</v>
+        <v>81.143202672</v>
       </c>
       <c r="Q64">
-        <v>82.423215328</v>
+        <v>82.143202672</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1225600249194815</v>
+        <v>0.124494594219214</v>
       </c>
       <c r="T64">
-        <v>1.056630635872523</v>
+        <v>1.083260710464865</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.690065389689547</v>
+        <v>5.599746891440508</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07532775986110918</v>
+        <v>0.07528247025281538</v>
       </c>
       <c r="C65">
-        <v>248.35587811917</v>
+        <v>242.4516005295173</v>
       </c>
       <c r="D65">
-        <v>489.7198781191699</v>
+        <v>489.8436005295172</v>
       </c>
       <c r="E65">
-        <v>116.564</v>
+        <v>122.592</v>
       </c>
       <c r="F65">
-        <v>379.764</v>
+        <v>385.792</v>
       </c>
       <c r="G65">
         <v>138.4</v>
@@ -6745,28 +6745,28 @@
         <v>117.6</v>
       </c>
       <c r="M65">
-        <v>21.0009492</v>
+        <v>21.3342976</v>
       </c>
       <c r="N65">
-        <v>96.5990508</v>
+        <v>96.2657024</v>
       </c>
       <c r="O65">
-        <v>15.455848128</v>
+        <v>15.402512384</v>
       </c>
       <c r="P65">
-        <v>81.143202672</v>
+        <v>80.86319001599999</v>
       </c>
       <c r="Q65">
-        <v>82.143202672</v>
+        <v>81.86319001599999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.124494594219214</v>
+        <v>0.1265366395911539</v>
       </c>
       <c r="T65">
-        <v>1.083260710464865</v>
+        <v>1.11137023364567</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.599746891440508</v>
+        <v>5.512250846261749</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07528247025281538</v>
+        <v>0.0752371806445216</v>
       </c>
       <c r="C66">
-        <v>242.4516005295173</v>
+        <v>236.5473854699094</v>
       </c>
       <c r="D66">
-        <v>489.8436005295172</v>
+        <v>489.9673854699094</v>
       </c>
       <c r="E66">
-        <v>122.592</v>
+        <v>128.62</v>
       </c>
       <c r="F66">
-        <v>385.792</v>
+        <v>391.82</v>
       </c>
       <c r="G66">
         <v>138.4</v>
@@ -6827,28 +6827,28 @@
         <v>117.6</v>
       </c>
       <c r="M66">
-        <v>21.3342976</v>
+        <v>21.667646</v>
       </c>
       <c r="N66">
-        <v>96.2657024</v>
+        <v>95.93235399999999</v>
       </c>
       <c r="O66">
-        <v>15.402512384</v>
+        <v>15.34917664</v>
       </c>
       <c r="P66">
-        <v>80.86319001599999</v>
+        <v>80.58317735999999</v>
       </c>
       <c r="Q66">
-        <v>81.86319001599999</v>
+        <v>81.58317735999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1265366395911539</v>
+        <v>0.1286953732700617</v>
       </c>
       <c r="T66">
-        <v>1.11137023364567</v>
+        <v>1.14108601529395</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.512250846261749</v>
+        <v>5.427446987088491</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0752371806445216</v>
+        <v>0.07519189103622781</v>
       </c>
       <c r="C67">
-        <v>236.5473854699094</v>
+        <v>230.6432329877633</v>
       </c>
       <c r="D67">
-        <v>489.9673854699094</v>
+        <v>490.0912329877632</v>
       </c>
       <c r="E67">
-        <v>128.62</v>
+        <v>134.648</v>
       </c>
       <c r="F67">
-        <v>391.82</v>
+        <v>397.848</v>
       </c>
       <c r="G67">
         <v>138.4</v>
@@ -6909,28 +6909,28 @@
         <v>117.6</v>
       </c>
       <c r="M67">
-        <v>21.667646</v>
+        <v>22.0009944</v>
       </c>
       <c r="N67">
-        <v>95.93235399999999</v>
+        <v>95.5990056</v>
       </c>
       <c r="O67">
-        <v>15.34917664</v>
+        <v>15.295840896</v>
       </c>
       <c r="P67">
-        <v>80.58317735999999</v>
+        <v>80.303164704</v>
       </c>
       <c r="Q67">
-        <v>81.58317735999999</v>
+        <v>81.303164704</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1286953732700617</v>
+        <v>0.130981091283023</v>
       </c>
       <c r="T67">
-        <v>1.14108601529395</v>
+        <v>1.172549784098011</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.427446987088491</v>
+        <v>5.345212941829574</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07519189103622781</v>
+        <v>0.07514660142793403</v>
       </c>
       <c r="C68">
-        <v>230.6432329877633</v>
+        <v>224.7391431305431</v>
       </c>
       <c r="D68">
-        <v>490.0912329877632</v>
+        <v>490.215143130543</v>
       </c>
       <c r="E68">
-        <v>134.648</v>
+        <v>140.676</v>
       </c>
       <c r="F68">
-        <v>397.848</v>
+        <v>403.876</v>
       </c>
       <c r="G68">
         <v>138.4</v>
@@ -6991,28 +6991,28 @@
         <v>117.6</v>
       </c>
       <c r="M68">
-        <v>22.0009944</v>
+        <v>22.3343428</v>
       </c>
       <c r="N68">
-        <v>95.5990056</v>
+        <v>95.26565719999999</v>
       </c>
       <c r="O68">
-        <v>15.295840896</v>
+        <v>15.242505152</v>
       </c>
       <c r="P68">
-        <v>80.303164704</v>
+        <v>80.02315204799999</v>
       </c>
       <c r="Q68">
-        <v>81.303164704</v>
+        <v>81.02315204799999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.130981091283023</v>
+        <v>0.1334053376604062</v>
       </c>
       <c r="T68">
-        <v>1.172549784098011</v>
+        <v>1.205920447981107</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.345212941829574</v>
+        <v>5.265433644190328</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07514660142793403</v>
+        <v>0.07510131181964022</v>
       </c>
       <c r="C69">
-        <v>224.7391431305431</v>
+        <v>218.8351159457616</v>
       </c>
       <c r="D69">
-        <v>490.215143130543</v>
+        <v>490.3391159457616</v>
       </c>
       <c r="E69">
-        <v>140.676</v>
+        <v>146.704</v>
       </c>
       <c r="F69">
-        <v>403.876</v>
+        <v>409.904</v>
       </c>
       <c r="G69">
         <v>138.4</v>
@@ -7073,28 +7073,28 @@
         <v>117.6</v>
       </c>
       <c r="M69">
-        <v>22.3343428</v>
+        <v>22.6676912</v>
       </c>
       <c r="N69">
-        <v>95.26565719999999</v>
+        <v>94.93230879999999</v>
       </c>
       <c r="O69">
-        <v>15.242505152</v>
+        <v>15.189169408</v>
       </c>
       <c r="P69">
-        <v>80.02315204799999</v>
+        <v>79.74313939199999</v>
       </c>
       <c r="Q69">
-        <v>81.02315204799999</v>
+        <v>80.74313939199999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1334053376604062</v>
+        <v>0.1359810994363757</v>
       </c>
       <c r="T69">
-        <v>1.205920447981107</v>
+        <v>1.241376778356895</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.265433644190328</v>
+        <v>5.188000796481646</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07510131181964022</v>
+        <v>0.07505602221134644</v>
       </c>
       <c r="C70">
-        <v>218.8351159457616</v>
+        <v>212.9311514809792</v>
       </c>
       <c r="D70">
-        <v>490.3391159457616</v>
+        <v>490.4631514809793</v>
       </c>
       <c r="E70">
-        <v>146.704</v>
+        <v>152.732</v>
       </c>
       <c r="F70">
-        <v>409.904</v>
+        <v>415.932</v>
       </c>
       <c r="G70">
         <v>138.4</v>
@@ -7155,28 +7155,28 @@
         <v>117.6</v>
       </c>
       <c r="M70">
-        <v>22.6676912</v>
+        <v>23.0010396</v>
       </c>
       <c r="N70">
-        <v>94.93230879999999</v>
+        <v>94.5989604</v>
       </c>
       <c r="O70">
-        <v>15.189169408</v>
+        <v>15.135833664</v>
       </c>
       <c r="P70">
-        <v>79.74313939199999</v>
+        <v>79.46312673599999</v>
       </c>
       <c r="Q70">
-        <v>80.74313939199999</v>
+        <v>80.46312673599999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1359810994363757</v>
+        <v>0.1387230393914402</v>
       </c>
       <c r="T70">
-        <v>1.241376778356895</v>
+        <v>1.279120613918219</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.188000796481646</v>
+        <v>5.112812379141332</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07505602221134644</v>
+        <v>0.07501073260305266</v>
       </c>
       <c r="C71">
-        <v>212.9311514809792</v>
+        <v>207.0272497838049</v>
       </c>
       <c r="D71">
-        <v>490.4631514809793</v>
+        <v>490.5872497838049</v>
       </c>
       <c r="E71">
-        <v>152.732</v>
+        <v>158.76</v>
       </c>
       <c r="F71">
-        <v>415.932</v>
+        <v>421.96</v>
       </c>
       <c r="G71">
         <v>138.4</v>
@@ -7237,28 +7237,28 @@
         <v>117.6</v>
       </c>
       <c r="M71">
-        <v>23.0010396</v>
+        <v>23.334388</v>
       </c>
       <c r="N71">
-        <v>94.5989604</v>
+        <v>94.26561199999999</v>
       </c>
       <c r="O71">
-        <v>15.135833664</v>
+        <v>15.08249792</v>
       </c>
       <c r="P71">
-        <v>79.46312673599999</v>
+        <v>79.18311408</v>
       </c>
       <c r="Q71">
-        <v>80.46312673599999</v>
+        <v>80.18311408</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1387230393914402</v>
+        <v>0.1416477753435089</v>
       </c>
       <c r="T71">
-        <v>1.279120613918219</v>
+        <v>1.31938070518363</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.112812379141332</v>
+        <v>5.039772202296455</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07501073260305266</v>
+        <v>0.07496544299475887</v>
       </c>
       <c r="C72">
-        <v>207.0272497838049</v>
+        <v>201.1234109018955</v>
       </c>
       <c r="D72">
-        <v>490.5872497838049</v>
+        <v>490.7114109018955</v>
       </c>
       <c r="E72">
-        <v>158.76</v>
+        <v>164.788</v>
       </c>
       <c r="F72">
-        <v>421.96</v>
+        <v>427.988</v>
       </c>
       <c r="G72">
         <v>138.4</v>
@@ -7319,28 +7319,28 @@
         <v>117.6</v>
       </c>
       <c r="M72">
-        <v>23.334388</v>
+        <v>23.6677364</v>
       </c>
       <c r="N72">
-        <v>94.26561199999999</v>
+        <v>93.9322636</v>
       </c>
       <c r="O72">
-        <v>15.08249792</v>
+        <v>15.029162176</v>
       </c>
       <c r="P72">
-        <v>79.18311408</v>
+        <v>78.903101424</v>
       </c>
       <c r="Q72">
-        <v>80.18311408</v>
+        <v>79.903101424</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1416477753435089</v>
+        <v>0.1447742172233065</v>
       </c>
       <c r="T72">
-        <v>1.31938070518363</v>
+        <v>1.362417354467346</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.039772202296455</v>
+        <v>4.968789495221857</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07496544299475888</v>
+        <v>0.07492015338646507</v>
       </c>
       <c r="C73">
-        <v>201.1234109018956</v>
+        <v>195.2196348829564</v>
       </c>
       <c r="D73">
-        <v>490.7114109018955</v>
+        <v>490.8356348829564</v>
       </c>
       <c r="E73">
-        <v>164.788</v>
+        <v>170.816</v>
       </c>
       <c r="F73">
-        <v>427.9879999999999</v>
+        <v>434.016</v>
       </c>
       <c r="G73">
         <v>138.4</v>
@@ -7401,28 +7401,28 @@
         <v>117.6</v>
       </c>
       <c r="M73">
-        <v>23.6677364</v>
+        <v>24.0010848</v>
       </c>
       <c r="N73">
-        <v>93.9322636</v>
+        <v>93.59891519999999</v>
       </c>
       <c r="O73">
-        <v>15.029162176</v>
+        <v>14.975826432</v>
       </c>
       <c r="P73">
-        <v>78.903101424</v>
+        <v>78.62308876799999</v>
       </c>
       <c r="Q73">
-        <v>79.903101424</v>
+        <v>79.62308876799999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1447742172233064</v>
+        <v>0.1481239763802324</v>
       </c>
       <c r="T73">
-        <v>1.362417354467345</v>
+        <v>1.40852805012847</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.968789495221858</v>
+        <v>4.899778530010444</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07492015338646507</v>
+        <v>0.07487486377817129</v>
       </c>
       <c r="C74">
-        <v>195.2196348829564</v>
+        <v>189.3159217747407</v>
       </c>
       <c r="D74">
-        <v>490.8356348829564</v>
+        <v>490.9599217747406</v>
       </c>
       <c r="E74">
-        <v>170.816</v>
+        <v>176.844</v>
       </c>
       <c r="F74">
-        <v>434.016</v>
+        <v>440.044</v>
       </c>
       <c r="G74">
         <v>138.4</v>
@@ -7483,28 +7483,28 @@
         <v>117.6</v>
       </c>
       <c r="M74">
-        <v>24.0010848</v>
+        <v>24.3344332</v>
       </c>
       <c r="N74">
-        <v>93.59891519999999</v>
+        <v>93.26556679999999</v>
       </c>
       <c r="O74">
-        <v>14.975826432</v>
+        <v>14.922490688</v>
       </c>
       <c r="P74">
-        <v>78.62308876799999</v>
+        <v>78.34307611199999</v>
       </c>
       <c r="Q74">
-        <v>79.62308876799999</v>
+        <v>79.34307611199999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1481239763802324</v>
+        <v>0.1517218658450789</v>
       </c>
       <c r="T74">
-        <v>1.40852805012847</v>
+        <v>1.458054352875603</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.899778530010444</v>
+        <v>4.832658276174683</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07487486377817129</v>
+        <v>0.0748295741698775</v>
       </c>
       <c r="C75">
-        <v>189.3159217747407</v>
+        <v>183.4122716250507</v>
       </c>
       <c r="D75">
-        <v>490.9599217747406</v>
+        <v>491.0842716250506</v>
       </c>
       <c r="E75">
-        <v>176.844</v>
+        <v>182.872</v>
       </c>
       <c r="F75">
-        <v>440.044</v>
+        <v>446.0719999999999</v>
       </c>
       <c r="G75">
         <v>138.4</v>
@@ -7565,28 +7565,28 @@
         <v>117.6</v>
       </c>
       <c r="M75">
-        <v>24.3344332</v>
+        <v>24.6677816</v>
       </c>
       <c r="N75">
-        <v>93.26556679999999</v>
+        <v>92.9322184</v>
       </c>
       <c r="O75">
-        <v>14.922490688</v>
+        <v>14.869154944</v>
       </c>
       <c r="P75">
-        <v>78.34307611199999</v>
+        <v>78.06306345599999</v>
       </c>
       <c r="Q75">
-        <v>79.34307611199999</v>
+        <v>79.06306345599999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1517218658450789</v>
+        <v>0.1555965160379904</v>
       </c>
       <c r="T75">
-        <v>1.458054352875603</v>
+        <v>1.511390371218669</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.832658276174683</v>
+        <v>4.767352083253405</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0748295741698775</v>
+        <v>0.07478428456158372</v>
       </c>
       <c r="C76">
-        <v>183.4122716250507</v>
+        <v>177.5086844817365</v>
       </c>
       <c r="D76">
-        <v>491.0842716250506</v>
+        <v>491.2086844817364</v>
       </c>
       <c r="E76">
-        <v>182.872</v>
+        <v>188.9</v>
       </c>
       <c r="F76">
-        <v>446.0719999999999</v>
+        <v>452.1</v>
       </c>
       <c r="G76">
         <v>138.4</v>
@@ -7647,28 +7647,28 @@
         <v>117.6</v>
       </c>
       <c r="M76">
-        <v>24.6677816</v>
+        <v>25.00113</v>
       </c>
       <c r="N76">
-        <v>92.9322184</v>
+        <v>92.59886999999999</v>
       </c>
       <c r="O76">
-        <v>14.869154944</v>
+        <v>14.8158192</v>
       </c>
       <c r="P76">
-        <v>78.06306345599999</v>
+        <v>77.7830508</v>
       </c>
       <c r="Q76">
-        <v>79.06306345599999</v>
+        <v>78.7830508</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1555965160379904</v>
+        <v>0.1597811382463349</v>
       </c>
       <c r="T76">
-        <v>1.511390371218669</v>
+        <v>1.568993271029181</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.767352083253405</v>
+        <v>4.703787388810025</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07478428456158372</v>
+        <v>0.07473899495328992</v>
       </c>
       <c r="C77">
-        <v>177.5086844817365</v>
+        <v>171.605160392697</v>
       </c>
       <c r="D77">
-        <v>491.2086844817364</v>
+        <v>491.333160392697</v>
       </c>
       <c r="E77">
-        <v>188.9</v>
+        <v>194.928</v>
       </c>
       <c r="F77">
-        <v>452.1</v>
+        <v>458.128</v>
       </c>
       <c r="G77">
         <v>138.4</v>
@@ -7729,28 +7729,28 @@
         <v>117.6</v>
       </c>
       <c r="M77">
-        <v>25.00113</v>
+        <v>25.3344784</v>
       </c>
       <c r="N77">
-        <v>92.59886999999999</v>
+        <v>92.2655216</v>
       </c>
       <c r="O77">
-        <v>14.8158192</v>
+        <v>14.762483456</v>
       </c>
       <c r="P77">
-        <v>77.7830508</v>
+        <v>77.503038144</v>
       </c>
       <c r="Q77">
-        <v>78.7830508</v>
+        <v>78.503038144</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1597811382463349</v>
+        <v>0.1643144789720414</v>
       </c>
       <c r="T77">
-        <v>1.568993271029181</v>
+        <v>1.63139641249057</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.703787388810025</v>
+        <v>4.641895449483577</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07473899495328992</v>
+        <v>0.07469370534499614</v>
       </c>
       <c r="C78">
-        <v>171.605160392697</v>
+        <v>165.7016994058797</v>
       </c>
       <c r="D78">
-        <v>491.333160392697</v>
+        <v>491.4576994058796</v>
       </c>
       <c r="E78">
-        <v>194.928</v>
+        <v>200.956</v>
       </c>
       <c r="F78">
-        <v>458.128</v>
+        <v>464.1559999999999</v>
       </c>
       <c r="G78">
         <v>138.4</v>
@@ -7811,28 +7811,28 @@
         <v>117.6</v>
       </c>
       <c r="M78">
-        <v>25.3344784</v>
+        <v>25.6678268</v>
       </c>
       <c r="N78">
-        <v>92.2655216</v>
+        <v>91.93217319999999</v>
       </c>
       <c r="O78">
-        <v>14.762483456</v>
+        <v>14.709147712</v>
       </c>
       <c r="P78">
-        <v>77.503038144</v>
+        <v>77.22302548799999</v>
       </c>
       <c r="Q78">
-        <v>78.503038144</v>
+        <v>78.22302548799999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1643144789720414</v>
+        <v>0.1692420232391136</v>
       </c>
       <c r="T78">
-        <v>1.63139641249057</v>
+        <v>1.699225914079034</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.641895449483577</v>
+        <v>4.581611092996779</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07469370534499614</v>
+        <v>0.07464841573670235</v>
       </c>
       <c r="C79">
-        <v>165.7016994058797</v>
+        <v>159.7983015692805</v>
       </c>
       <c r="D79">
-        <v>491.4576994058796</v>
+        <v>491.5823015692805</v>
       </c>
       <c r="E79">
-        <v>200.956</v>
+        <v>206.984</v>
       </c>
       <c r="F79">
-        <v>464.1559999999999</v>
+        <v>470.184</v>
       </c>
       <c r="G79">
         <v>138.4</v>
@@ -7893,28 +7893,28 @@
         <v>117.6</v>
       </c>
       <c r="M79">
-        <v>25.6678268</v>
+        <v>26.0011752</v>
       </c>
       <c r="N79">
-        <v>91.93217319999999</v>
+        <v>91.59882479999999</v>
       </c>
       <c r="O79">
-        <v>14.709147712</v>
+        <v>14.655811968</v>
       </c>
       <c r="P79">
-        <v>77.22302548799999</v>
+        <v>76.94301283199999</v>
       </c>
       <c r="Q79">
-        <v>78.22302548799999</v>
+        <v>77.94301283199999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1692420232391136</v>
+        <v>0.1746175260759198</v>
       </c>
       <c r="T79">
-        <v>1.699225914079034</v>
+        <v>1.773221733993724</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.581611092996779</v>
+        <v>4.52287248924041</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07464841573670235</v>
+        <v>0.07626212612840857</v>
       </c>
       <c r="C80">
-        <v>159.7983015692805</v>
+        <v>149.3692441887564</v>
       </c>
       <c r="D80">
-        <v>491.5823015692805</v>
+        <v>487.1812441887564</v>
       </c>
       <c r="E80">
-        <v>206.984</v>
+        <v>213.012</v>
       </c>
       <c r="F80">
-        <v>470.184</v>
+        <v>476.212</v>
       </c>
       <c r="G80">
         <v>138.4</v>
@@ -7975,45 +7975,45 @@
         <v>117.6</v>
       </c>
       <c r="M80">
-        <v>26.0011752</v>
+        <v>27.5250536</v>
       </c>
       <c r="N80">
-        <v>91.59882479999999</v>
+        <v>90.07494639999999</v>
       </c>
       <c r="O80">
-        <v>14.655811968</v>
+        <v>14.411991424</v>
       </c>
       <c r="P80">
-        <v>76.94301283199999</v>
+        <v>75.66295497599999</v>
       </c>
       <c r="Q80">
-        <v>77.94301283199999</v>
+        <v>76.66295497599999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1746175260759198</v>
+        <v>0.1805049815638503</v>
       </c>
       <c r="T80">
-        <v>1.773221733993724</v>
+        <v>1.854264774852669</v>
       </c>
       <c r="U80">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V80">
         <v>0.16</v>
       </c>
       <c r="W80">
-        <v>0.046452</v>
+        <v>0.048552</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y80">
-        <v>4.52287248924041</v>
+        <v>4.272471244161355</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07626212612840857</v>
+        <v>0.07623783652011477</v>
       </c>
       <c r="C81">
-        <v>149.3692441887564</v>
+        <v>143.4069047811669</v>
       </c>
       <c r="D81">
-        <v>487.1812441887564</v>
+        <v>487.2469047811669</v>
       </c>
       <c r="E81">
-        <v>213.012</v>
+        <v>219.04</v>
       </c>
       <c r="F81">
-        <v>476.212</v>
+        <v>482.24</v>
       </c>
       <c r="G81">
         <v>138.4</v>
@@ -8057,28 +8057,28 @@
         <v>117.6</v>
       </c>
       <c r="M81">
-        <v>27.5250536</v>
+        <v>27.873472</v>
       </c>
       <c r="N81">
-        <v>90.07494639999999</v>
+        <v>89.72652799999999</v>
       </c>
       <c r="O81">
-        <v>14.411991424</v>
+        <v>14.35624448</v>
       </c>
       <c r="P81">
-        <v>75.66295497599999</v>
+        <v>75.37028351999999</v>
       </c>
       <c r="Q81">
-        <v>76.66295497599999</v>
+        <v>76.37028351999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1805049815638503</v>
+        <v>0.1869811826005739</v>
       </c>
       <c r="T81">
-        <v>1.854264774852669</v>
+        <v>1.943412119797509</v>
       </c>
       <c r="U81">
         <v>0.0578</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.272471244161355</v>
+        <v>4.219065353609338</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07623783652011477</v>
+        <v>0.076213546911821</v>
       </c>
       <c r="C82">
-        <v>143.4069047811669</v>
+        <v>137.4445830749752</v>
       </c>
       <c r="D82">
-        <v>487.2469047811669</v>
+        <v>487.3125830749752</v>
       </c>
       <c r="E82">
-        <v>219.04</v>
+        <v>225.068</v>
       </c>
       <c r="F82">
-        <v>482.24</v>
+        <v>488.268</v>
       </c>
       <c r="G82">
         <v>138.4</v>
@@ -8139,28 +8139,28 @@
         <v>117.6</v>
       </c>
       <c r="M82">
-        <v>27.873472</v>
+        <v>28.2218904</v>
       </c>
       <c r="N82">
-        <v>89.72652799999999</v>
+        <v>89.37810959999999</v>
       </c>
       <c r="O82">
-        <v>14.35624448</v>
+        <v>14.300497536</v>
       </c>
       <c r="P82">
-        <v>75.37028351999999</v>
+        <v>75.07761206399999</v>
       </c>
       <c r="Q82">
-        <v>76.37028351999999</v>
+        <v>76.07761206399999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1869811826005739</v>
+        <v>0.1941390890095842</v>
       </c>
       <c r="T82">
-        <v>1.943412119797509</v>
+        <v>2.041943395789175</v>
       </c>
       <c r="U82">
         <v>0.0578</v>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.219065353609338</v>
+        <v>4.166978127021569</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.076213546911821</v>
+        <v>0.0761892573035272</v>
       </c>
       <c r="C83">
-        <v>137.4445830749752</v>
+        <v>131.4822790773407</v>
       </c>
       <c r="D83">
-        <v>487.3125830749752</v>
+        <v>487.3782790773407</v>
       </c>
       <c r="E83">
-        <v>225.068</v>
+        <v>231.096</v>
       </c>
       <c r="F83">
-        <v>488.268</v>
+        <v>494.296</v>
       </c>
       <c r="G83">
         <v>138.4</v>
@@ -8221,28 +8221,28 @@
         <v>117.6</v>
       </c>
       <c r="M83">
-        <v>28.2218904</v>
+        <v>28.5703088</v>
       </c>
       <c r="N83">
-        <v>89.37810959999999</v>
+        <v>89.02969119999999</v>
       </c>
       <c r="O83">
-        <v>14.300497536</v>
+        <v>14.244750592</v>
       </c>
       <c r="P83">
-        <v>75.07761206399999</v>
+        <v>74.78494060799999</v>
       </c>
       <c r="Q83">
-        <v>76.07761206399999</v>
+        <v>75.78494060799999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1941390890095842</v>
+        <v>0.2020923183529289</v>
       </c>
       <c r="T83">
-        <v>2.041943395789175</v>
+        <v>2.151422591335469</v>
       </c>
       <c r="U83">
         <v>0.0578</v>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.166978127021569</v>
+        <v>4.116161320594475</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.0761892573035272</v>
+        <v>0.07616496769523341</v>
       </c>
       <c r="C84">
-        <v>131.4822790773407</v>
+        <v>125.5199927954262</v>
       </c>
       <c r="D84">
-        <v>487.3782790773407</v>
+        <v>487.4439927954262</v>
       </c>
       <c r="E84">
-        <v>231.096</v>
+        <v>237.124</v>
       </c>
       <c r="F84">
-        <v>494.296</v>
+        <v>500.324</v>
       </c>
       <c r="G84">
         <v>138.4</v>
@@ -8303,28 +8303,28 @@
         <v>117.6</v>
       </c>
       <c r="M84">
-        <v>28.5703088</v>
+        <v>28.9187272</v>
       </c>
       <c r="N84">
-        <v>89.02969119999999</v>
+        <v>88.68127279999999</v>
       </c>
       <c r="O84">
-        <v>14.244750592</v>
+        <v>14.189003648</v>
       </c>
       <c r="P84">
-        <v>74.78494060799999</v>
+        <v>74.49226915199999</v>
       </c>
       <c r="Q84">
-        <v>75.78494060799999</v>
+        <v>75.49226915199999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2020923183529289</v>
+        <v>0.2109812217366672</v>
       </c>
       <c r="T84">
-        <v>2.151422591335469</v>
+        <v>2.273781692240151</v>
       </c>
       <c r="U84">
         <v>0.0578</v>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.116161320594475</v>
+        <v>4.066569015527072</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07616496769523341</v>
+        <v>0.07614067808693963</v>
       </c>
       <c r="C85">
-        <v>125.5199927954262</v>
+        <v>119.5577242363987</v>
       </c>
       <c r="D85">
-        <v>487.4439927954262</v>
+        <v>487.5097242363987</v>
       </c>
       <c r="E85">
-        <v>237.124</v>
+        <v>243.152</v>
       </c>
       <c r="F85">
-        <v>500.324</v>
+        <v>506.352</v>
       </c>
       <c r="G85">
         <v>138.4</v>
@@ -8385,28 +8385,28 @@
         <v>117.6</v>
       </c>
       <c r="M85">
-        <v>28.9187272</v>
+        <v>29.2671456</v>
       </c>
       <c r="N85">
-        <v>88.68127279999999</v>
+        <v>88.33285439999999</v>
       </c>
       <c r="O85">
-        <v>14.189003648</v>
+        <v>14.133256704</v>
       </c>
       <c r="P85">
-        <v>74.49226915199999</v>
+        <v>74.19959769599998</v>
       </c>
       <c r="Q85">
-        <v>75.49226915199999</v>
+        <v>75.19959769599998</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2109812217366672</v>
+        <v>0.2209812380433727</v>
       </c>
       <c r="T85">
-        <v>2.273781692240151</v>
+        <v>2.411435680757919</v>
       </c>
       <c r="U85">
         <v>0.0578</v>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.066569015527072</v>
+        <v>4.018157479627941</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07614067808693963</v>
+        <v>0.07861538847864583</v>
       </c>
       <c r="C86">
-        <v>119.5577242363988</v>
+        <v>106.9226457231686</v>
       </c>
       <c r="D86">
-        <v>487.5097242363987</v>
+        <v>480.9026457231685</v>
       </c>
       <c r="E86">
-        <v>243.1519999999999</v>
+        <v>249.18</v>
       </c>
       <c r="F86">
-        <v>506.3519999999999</v>
+        <v>512.38</v>
       </c>
       <c r="G86">
         <v>138.4</v>
@@ -8467,45 +8467,45 @@
         <v>117.6</v>
       </c>
       <c r="M86">
-        <v>29.2671456</v>
+        <v>31.408894</v>
       </c>
       <c r="N86">
-        <v>88.3328544</v>
+        <v>86.19110599999999</v>
       </c>
       <c r="O86">
-        <v>14.133256704</v>
+        <v>13.79057696</v>
       </c>
       <c r="P86">
-        <v>74.199597696</v>
+        <v>72.40052904</v>
       </c>
       <c r="Q86">
-        <v>75.199597696</v>
+        <v>73.40052904</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2209812380433726</v>
+        <v>0.2323145898576388</v>
       </c>
       <c r="T86">
-        <v>2.411435680757918</v>
+        <v>2.567443534411388</v>
       </c>
       <c r="U86">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V86">
         <v>0.16</v>
       </c>
       <c r="W86">
-        <v>0.048552</v>
+        <v>0.051492</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y86">
-        <v>4.018157479627942</v>
+        <v>3.74416240189801</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07861538847864583</v>
+        <v>0.07862049887035204</v>
       </c>
       <c r="C87">
-        <v>106.9226457231686</v>
+        <v>100.8811870885035</v>
       </c>
       <c r="D87">
-        <v>480.9026457231685</v>
+        <v>480.8891870885033</v>
       </c>
       <c r="E87">
-        <v>249.18</v>
+        <v>255.2079999999999</v>
       </c>
       <c r="F87">
-        <v>512.38</v>
+        <v>518.4079999999999</v>
       </c>
       <c r="G87">
         <v>138.4</v>
@@ -8549,28 +8549,28 @@
         <v>117.6</v>
       </c>
       <c r="M87">
-        <v>31.408894</v>
+        <v>31.77841039999999</v>
       </c>
       <c r="N87">
-        <v>86.19110599999999</v>
+        <v>85.8215896</v>
       </c>
       <c r="O87">
-        <v>13.79057696</v>
+        <v>13.731454336</v>
       </c>
       <c r="P87">
-        <v>72.40052904</v>
+        <v>72.090135264</v>
       </c>
       <c r="Q87">
-        <v>73.40052904</v>
+        <v>73.090135264</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2323145898576388</v>
+        <v>0.245266991931086</v>
       </c>
       <c r="T87">
-        <v>2.567443534411388</v>
+        <v>2.745738224301067</v>
       </c>
       <c r="U87">
         <v>0.0613</v>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.74416240189801</v>
+        <v>3.700625629782917</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07862049887035204</v>
+        <v>0.07862560926205825</v>
       </c>
       <c r="C88">
-        <v>100.8811870885035</v>
+        <v>94.83972920712904</v>
       </c>
       <c r="D88">
-        <v>480.8891870885033</v>
+        <v>480.8757292071289</v>
       </c>
       <c r="E88">
-        <v>255.2079999999999</v>
+        <v>261.2359999999999</v>
       </c>
       <c r="F88">
-        <v>518.4079999999999</v>
+        <v>524.4359999999999</v>
       </c>
       <c r="G88">
         <v>138.4</v>
@@ -8631,28 +8631,28 @@
         <v>117.6</v>
       </c>
       <c r="M88">
-        <v>31.77841039999999</v>
+        <v>32.14792679999999</v>
       </c>
       <c r="N88">
-        <v>85.8215896</v>
+        <v>85.4520732</v>
       </c>
       <c r="O88">
-        <v>13.731454336</v>
+        <v>13.672331712</v>
       </c>
       <c r="P88">
-        <v>72.090135264</v>
+        <v>71.779741488</v>
       </c>
       <c r="Q88">
-        <v>73.090135264</v>
+        <v>72.779741488</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.245266991931086</v>
+        <v>0.2602120712466019</v>
       </c>
       <c r="T88">
-        <v>2.745738224301067</v>
+        <v>2.951462866481467</v>
       </c>
       <c r="U88">
         <v>0.0613</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.700625629782917</v>
+        <v>3.658089703003804</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07862560926205825</v>
+        <v>0.07863071965376446</v>
       </c>
       <c r="C89">
-        <v>94.83972920712904</v>
+        <v>88.79827207898222</v>
       </c>
       <c r="D89">
-        <v>480.8757292071289</v>
+        <v>480.8622720789821</v>
       </c>
       <c r="E89">
-        <v>261.2359999999999</v>
+        <v>267.264</v>
       </c>
       <c r="F89">
-        <v>524.4359999999999</v>
+        <v>530.4639999999999</v>
       </c>
       <c r="G89">
         <v>138.4</v>
@@ -8713,28 +8713,28 @@
         <v>117.6</v>
       </c>
       <c r="M89">
-        <v>32.14792679999999</v>
+        <v>32.5174432</v>
       </c>
       <c r="N89">
-        <v>85.4520732</v>
+        <v>85.08255679999999</v>
       </c>
       <c r="O89">
-        <v>13.672331712</v>
+        <v>13.613209088</v>
       </c>
       <c r="P89">
-        <v>71.779741488</v>
+        <v>71.46934771199999</v>
       </c>
       <c r="Q89">
-        <v>72.779741488</v>
+        <v>72.46934771199999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2602120712466019</v>
+        <v>0.2776479971147038</v>
       </c>
       <c r="T89">
-        <v>2.951462866481467</v>
+        <v>3.191474949025267</v>
       </c>
       <c r="U89">
         <v>0.0613</v>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.658089703003804</v>
+        <v>3.616520501833306</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07863071965376446</v>
+        <v>0.07863583004547067</v>
       </c>
       <c r="C90">
-        <v>88.79827207898222</v>
+        <v>82.75681570399979</v>
       </c>
       <c r="D90">
-        <v>480.8622720789821</v>
+        <v>480.8488157039997</v>
       </c>
       <c r="E90">
-        <v>267.264</v>
+        <v>273.292</v>
       </c>
       <c r="F90">
-        <v>530.4639999999999</v>
+        <v>536.492</v>
       </c>
       <c r="G90">
         <v>138.4</v>
@@ -8795,28 +8795,28 @@
         <v>117.6</v>
       </c>
       <c r="M90">
-        <v>32.5174432</v>
+        <v>32.8869596</v>
       </c>
       <c r="N90">
-        <v>85.08255679999999</v>
+        <v>84.7130404</v>
       </c>
       <c r="O90">
-        <v>13.613209088</v>
+        <v>13.554086464</v>
       </c>
       <c r="P90">
-        <v>71.46934771199999</v>
+        <v>71.158953936</v>
       </c>
       <c r="Q90">
-        <v>72.46934771199999</v>
+        <v>72.158953936</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2776479971147038</v>
+        <v>0.2982540913224607</v>
       </c>
       <c r="T90">
-        <v>3.191474949025267</v>
+        <v>3.475125592031576</v>
       </c>
       <c r="U90">
         <v>0.0613</v>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.616520501833306</v>
+        <v>3.575885440014954</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07863583004547067</v>
+        <v>0.07864094043717688</v>
       </c>
       <c r="C91">
-        <v>82.75681570399979</v>
+        <v>76.71536008211842</v>
       </c>
       <c r="D91">
-        <v>480.8488157039997</v>
+        <v>480.8353600821184</v>
       </c>
       <c r="E91">
-        <v>273.292</v>
+        <v>279.32</v>
       </c>
       <c r="F91">
-        <v>536.492</v>
+        <v>542.52</v>
       </c>
       <c r="G91">
         <v>138.4</v>
@@ -8877,28 +8877,28 @@
         <v>117.6</v>
       </c>
       <c r="M91">
-        <v>32.8869596</v>
+        <v>33.256476</v>
       </c>
       <c r="N91">
-        <v>84.7130404</v>
+        <v>84.343524</v>
       </c>
       <c r="O91">
-        <v>13.554086464</v>
+        <v>13.49496384</v>
       </c>
       <c r="P91">
-        <v>71.158953936</v>
+        <v>70.84856016000001</v>
       </c>
       <c r="Q91">
-        <v>72.158953936</v>
+        <v>71.84856016000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2982540913224607</v>
+        <v>0.3229814043717689</v>
       </c>
       <c r="T91">
-        <v>3.475125592031576</v>
+        <v>3.815506363639147</v>
       </c>
       <c r="U91">
         <v>0.0613</v>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.575885440014954</v>
+        <v>3.536153379570343</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07864094043717688</v>
+        <v>0.0807863708288831</v>
       </c>
       <c r="C92">
-        <v>76.71536008211842</v>
+        <v>65.10420612190455</v>
       </c>
       <c r="D92">
-        <v>480.8353600821184</v>
+        <v>475.2522061219046</v>
       </c>
       <c r="E92">
-        <v>279.32</v>
+        <v>285.348</v>
       </c>
       <c r="F92">
-        <v>542.52</v>
+        <v>548.548</v>
       </c>
       <c r="G92">
         <v>138.4</v>
@@ -8959,45 +8959,45 @@
         <v>117.6</v>
       </c>
       <c r="M92">
-        <v>33.256476</v>
+        <v>35.1619268</v>
       </c>
       <c r="N92">
-        <v>84.343524</v>
+        <v>82.43807319999999</v>
       </c>
       <c r="O92">
-        <v>13.49496384</v>
+        <v>13.190091712</v>
       </c>
       <c r="P92">
-        <v>70.84856016000001</v>
+        <v>69.24798148799999</v>
       </c>
       <c r="Q92">
-        <v>71.84856016000001</v>
+        <v>70.24798148799999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3229814043717689</v>
+        <v>0.3532036758764789</v>
       </c>
       <c r="T92">
-        <v>3.815506363639147</v>
+        <v>4.231527306715066</v>
       </c>
       <c r="U92">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V92">
         <v>0.16</v>
       </c>
       <c r="W92">
-        <v>0.051492</v>
+        <v>0.053844</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y92">
-        <v>3.536153379570343</v>
+        <v>3.344526614508508</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.0807863708288831</v>
+        <v>0.08081500122058932</v>
       </c>
       <c r="C93">
-        <v>65.10420612190455</v>
+        <v>59.00257644073633</v>
       </c>
       <c r="D93">
-        <v>475.2522061219046</v>
+        <v>475.1785764407364</v>
       </c>
       <c r="E93">
-        <v>285.348</v>
+        <v>291.376</v>
       </c>
       <c r="F93">
-        <v>548.548</v>
+        <v>554.576</v>
       </c>
       <c r="G93">
         <v>138.4</v>
@@ -9041,28 +9041,28 @@
         <v>117.6</v>
       </c>
       <c r="M93">
-        <v>35.1619268</v>
+        <v>35.5483216</v>
       </c>
       <c r="N93">
-        <v>82.43807319999999</v>
+        <v>82.05167839999999</v>
       </c>
       <c r="O93">
-        <v>13.190091712</v>
+        <v>13.128268544</v>
       </c>
       <c r="P93">
-        <v>69.24798148799999</v>
+        <v>68.92340985599999</v>
       </c>
       <c r="Q93">
-        <v>70.24798148799999</v>
+        <v>69.92340985599999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3532036758764789</v>
+        <v>0.3909815152573665</v>
       </c>
       <c r="T93">
-        <v>4.231527306715066</v>
+        <v>4.751553485559967</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.344526614508508</v>
+        <v>3.308173064350807</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08081500122058932</v>
+        <v>0.08084363161229552</v>
       </c>
       <c r="C94">
-        <v>59.00257644073633</v>
+        <v>52.90096957057301</v>
       </c>
       <c r="D94">
-        <v>475.1785764407364</v>
+        <v>475.1049695705731</v>
       </c>
       <c r="E94">
-        <v>291.376</v>
+        <v>297.4040000000001</v>
       </c>
       <c r="F94">
-        <v>554.576</v>
+        <v>560.604</v>
       </c>
       <c r="G94">
         <v>138.4</v>
@@ -9123,28 +9123,28 @@
         <v>117.6</v>
       </c>
       <c r="M94">
-        <v>35.5483216</v>
+        <v>35.93471640000001</v>
       </c>
       <c r="N94">
-        <v>82.05167839999999</v>
+        <v>81.66528359999998</v>
       </c>
       <c r="O94">
-        <v>13.128268544</v>
+        <v>13.066445376</v>
       </c>
       <c r="P94">
-        <v>68.92340985599999</v>
+        <v>68.59883822399999</v>
       </c>
       <c r="Q94">
-        <v>69.92340985599999</v>
+        <v>69.59883822399999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3909815152573665</v>
+        <v>0.4395530230327934</v>
       </c>
       <c r="T94">
-        <v>4.751553485559967</v>
+        <v>5.420158572646266</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.308173064350807</v>
+        <v>3.27260131097069</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08084363161229552</v>
+        <v>0.08087226200400173</v>
       </c>
       <c r="C95">
-        <v>52.90096957057301</v>
+        <v>46.79938550081567</v>
       </c>
       <c r="D95">
-        <v>475.1049695705731</v>
+        <v>475.0313855008156</v>
       </c>
       <c r="E95">
-        <v>297.4040000000001</v>
+        <v>303.432</v>
       </c>
       <c r="F95">
-        <v>560.604</v>
+        <v>566.6319999999999</v>
       </c>
       <c r="G95">
         <v>138.4</v>
@@ -9205,28 +9205,28 @@
         <v>117.6</v>
       </c>
       <c r="M95">
-        <v>35.93471640000001</v>
+        <v>36.3211112</v>
       </c>
       <c r="N95">
-        <v>81.66528359999998</v>
+        <v>81.2788888</v>
       </c>
       <c r="O95">
-        <v>13.066445376</v>
+        <v>13.004622208</v>
       </c>
       <c r="P95">
-        <v>68.59883822399999</v>
+        <v>68.274266592</v>
       </c>
       <c r="Q95">
-        <v>69.59883822399999</v>
+        <v>69.274266592</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4395530230327934</v>
+        <v>0.5043150334000293</v>
       </c>
       <c r="T95">
-        <v>5.420158572646266</v>
+        <v>6.311632022094668</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.27260131097069</v>
+        <v>3.237786403407174</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08087226200400173</v>
+        <v>0.08090089239570794</v>
       </c>
       <c r="C96">
-        <v>46.79938550081567</v>
+        <v>40.69782422087167</v>
       </c>
       <c r="D96">
-        <v>475.0313855008156</v>
+        <v>474.9578242208716</v>
       </c>
       <c r="E96">
-        <v>303.432</v>
+        <v>309.46</v>
       </c>
       <c r="F96">
-        <v>566.6319999999999</v>
+        <v>572.66</v>
       </c>
       <c r="G96">
         <v>138.4</v>
@@ -9287,28 +9287,28 @@
         <v>117.6</v>
       </c>
       <c r="M96">
-        <v>36.3211112</v>
+        <v>36.707506</v>
       </c>
       <c r="N96">
-        <v>81.2788888</v>
+        <v>80.892494</v>
       </c>
       <c r="O96">
-        <v>13.004622208</v>
+        <v>12.94279904</v>
       </c>
       <c r="P96">
-        <v>68.274266592</v>
+        <v>67.94969496</v>
       </c>
       <c r="Q96">
-        <v>69.274266592</v>
+        <v>68.94969496</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5043150334000293</v>
+        <v>0.5949818479141595</v>
       </c>
       <c r="T96">
-        <v>6.311632022094668</v>
+        <v>7.55969485132243</v>
       </c>
       <c r="U96">
         <v>0.0641</v>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.237786403407174</v>
+        <v>3.203704441266045</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08090089239570794</v>
+        <v>0.08092952278741415</v>
       </c>
       <c r="C97">
-        <v>40.69782422087167</v>
+        <v>34.59628572015549</v>
       </c>
       <c r="D97">
-        <v>474.9578242208716</v>
+        <v>474.8842857201554</v>
       </c>
       <c r="E97">
-        <v>309.46</v>
+        <v>315.488</v>
       </c>
       <c r="F97">
-        <v>572.66</v>
+        <v>578.688</v>
       </c>
       <c r="G97">
         <v>138.4</v>
@@ -9369,28 +9369,28 @@
         <v>117.6</v>
       </c>
       <c r="M97">
-        <v>36.707506</v>
+        <v>37.0939008</v>
       </c>
       <c r="N97">
-        <v>80.892494</v>
+        <v>80.50609919999999</v>
       </c>
       <c r="O97">
-        <v>12.94279904</v>
+        <v>12.880975872</v>
       </c>
       <c r="P97">
-        <v>67.94969496</v>
+        <v>67.625123328</v>
       </c>
       <c r="Q97">
-        <v>68.94969496</v>
+        <v>68.625123328</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5949818479141595</v>
+        <v>0.7309820696853551</v>
       </c>
       <c r="T97">
-        <v>7.55969485132243</v>
+        <v>9.431789095164074</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.203704441266045</v>
+        <v>3.170332520002857</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08092952278741415</v>
+        <v>0.08095815317912036</v>
       </c>
       <c r="C98">
-        <v>34.59628572015549</v>
+        <v>28.49476998808802</v>
       </c>
       <c r="D98">
-        <v>474.8842857201554</v>
+        <v>474.8107699880879</v>
       </c>
       <c r="E98">
-        <v>315.488</v>
+        <v>321.5159999999999</v>
       </c>
       <c r="F98">
-        <v>578.688</v>
+        <v>584.7159999999999</v>
       </c>
       <c r="G98">
         <v>138.4</v>
@@ -9451,28 +9451,28 @@
         <v>117.6</v>
       </c>
       <c r="M98">
-        <v>37.0939008</v>
+        <v>37.4802956</v>
       </c>
       <c r="N98">
-        <v>80.50609919999999</v>
+        <v>80.11970439999999</v>
       </c>
       <c r="O98">
-        <v>12.880975872</v>
+        <v>12.819152704</v>
       </c>
       <c r="P98">
-        <v>67.625123328</v>
+        <v>67.30055169599999</v>
       </c>
       <c r="Q98">
-        <v>68.625123328</v>
+        <v>68.30055169599999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7309820696853533</v>
+        <v>0.9576491059706781</v>
       </c>
       <c r="T98">
-        <v>9.431789095164049</v>
+        <v>12.55194616823344</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.170332520002857</v>
+        <v>3.137648679590456</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08095815317912036</v>
+        <v>0.08098678357082657</v>
       </c>
       <c r="C99">
-        <v>28.49476998808802</v>
+        <v>22.3932770140965</v>
       </c>
       <c r="D99">
-        <v>474.8107699880879</v>
+        <v>474.7372770140964</v>
       </c>
       <c r="E99">
-        <v>321.5159999999999</v>
+        <v>327.5439999999999</v>
       </c>
       <c r="F99">
-        <v>584.7159999999999</v>
+        <v>590.7439999999999</v>
       </c>
       <c r="G99">
         <v>138.4</v>
@@ -9533,28 +9533,28 @@
         <v>117.6</v>
       </c>
       <c r="M99">
-        <v>37.4802956</v>
+        <v>37.8666904</v>
       </c>
       <c r="N99">
-        <v>80.11970439999999</v>
+        <v>79.7333096</v>
       </c>
       <c r="O99">
-        <v>12.819152704</v>
+        <v>12.757329536</v>
       </c>
       <c r="P99">
-        <v>67.30055169599999</v>
+        <v>66.975980064</v>
       </c>
       <c r="Q99">
-        <v>68.30055169599999</v>
+        <v>67.975980064</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9576491059706781</v>
+        <v>1.410983178541328</v>
       </c>
       <c r="T99">
-        <v>12.55194616823344</v>
+        <v>18.79226031437222</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.137648679590456</v>
+        <v>3.105631856329329</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08098678357082657</v>
+        <v>0.08101541396253278</v>
       </c>
       <c r="C100">
-        <v>22.3932770140965</v>
+        <v>16.29180678761475</v>
       </c>
       <c r="D100">
-        <v>474.7372770140964</v>
+        <v>474.6638067876146</v>
       </c>
       <c r="E100">
-        <v>327.5439999999999</v>
+        <v>333.5719999999999</v>
       </c>
       <c r="F100">
-        <v>590.7439999999999</v>
+        <v>596.7719999999999</v>
       </c>
       <c r="G100">
         <v>138.4</v>
@@ -9615,28 +9615,28 @@
         <v>117.6</v>
       </c>
       <c r="M100">
-        <v>37.8666904</v>
+        <v>38.2530852</v>
       </c>
       <c r="N100">
-        <v>79.7333096</v>
+        <v>79.34691479999999</v>
       </c>
       <c r="O100">
-        <v>12.757329536</v>
+        <v>12.695506368</v>
       </c>
       <c r="P100">
-        <v>66.975980064</v>
+        <v>66.651408432</v>
       </c>
       <c r="Q100">
-        <v>67.975980064</v>
+        <v>67.651408432</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.410983178541328</v>
+        <v>2.770985396253276</v>
       </c>
       <c r="T100">
-        <v>18.79226031437222</v>
+        <v>37.51320275278858</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.105631856329329</v>
+        <v>3.074261837578528</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08101541396253278</v>
-      </c>
-      <c r="C101">
-        <v>16.29180678761475</v>
-      </c>
-      <c r="D101">
-        <v>474.6638067876146</v>
-      </c>
-      <c r="E101">
-        <v>333.5719999999999</v>
-      </c>
-      <c r="F101">
-        <v>596.7719999999999</v>
-      </c>
-      <c r="G101">
-        <v>138.4</v>
-      </c>
-      <c r="H101">
-        <v>339.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>118.6</v>
-      </c>
-      <c r="K101">
-        <v>1</v>
-      </c>
-      <c r="L101">
-        <v>117.6</v>
-      </c>
-      <c r="M101">
-        <v>38.2530852</v>
-      </c>
-      <c r="N101">
-        <v>79.34691479999999</v>
-      </c>
-      <c r="O101">
-        <v>12.695506368</v>
-      </c>
-      <c r="P101">
-        <v>66.651408432</v>
-      </c>
-      <c r="Q101">
-        <v>67.651408432</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.770985396253276</v>
-      </c>
-      <c r="T101">
-        <v>37.51320275278858</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.16</v>
-      </c>
-      <c r="W101">
-        <v>0.053844</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.074261837578528</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
